--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F8C8DE-F3BE-4E7B-8C20-DB056B9A3189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4750BD56-567F-4998-9B34-817586B54504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="33615" yWindow="1725" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="10" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida" sheetId="1" r:id="rId1"/>
     <sheet name="Pizza Teste" sheetId="6" r:id="rId2"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId3"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId4"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId5"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId6"/>
+    <sheet name="slide_8" sheetId="7" r:id="rId3"/>
+    <sheet name="slide_9" sheetId="8" r:id="rId4"/>
+    <sheet name="slide_11" sheetId="9" r:id="rId5"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId6"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId7"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId8"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId9"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId10"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId11"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId12"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId13"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId14"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="122">
   <si>
     <t>Labels</t>
   </si>
@@ -194,14 +203,231 @@
   </si>
   <si>
     <t>Destaques do Trimestre</t>
+  </si>
+  <si>
+    <t>Receitas Totais</t>
+  </si>
+  <si>
+    <t>bilhoes</t>
+  </si>
+  <si>
+    <t>Graficos de Receitas totais</t>
+  </si>
+  <si>
+    <t>Margem Financeira Bruta</t>
+  </si>
+  <si>
+    <t>Serviços e Seguros</t>
+  </si>
+  <si>
+    <t>Margem Financeira Bruta Total</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>clientes</t>
+  </si>
+  <si>
+    <t>Receitas De Serviços e Correetagem</t>
+  </si>
+  <si>
+    <t>Seguros</t>
+  </si>
+  <si>
+    <t>Servicos e Tarifas</t>
+  </si>
+  <si>
+    <t>Custo de Crédito / Carteira de Crédito</t>
+  </si>
+  <si>
+    <t>PDD Expandida</t>
+  </si>
+  <si>
+    <t>Rec. De crédito</t>
+  </si>
+  <si>
+    <t>Custo de Crédito Sobre Carteira</t>
+  </si>
+  <si>
+    <t>Indice de Cobertura</t>
+  </si>
+  <si>
+    <t>Despesa Pessoal Administrativa</t>
+  </si>
+  <si>
+    <t>Pessoal</t>
+  </si>
+  <si>
+    <t>Administrativas</t>
+  </si>
+  <si>
+    <t>Deprec. Amortiza.</t>
+  </si>
+  <si>
+    <t>Indice de Eficiencia</t>
+  </si>
+  <si>
+    <t>Emprestimos</t>
+  </si>
+  <si>
+    <t>Paineis Solares</t>
+  </si>
+  <si>
+    <t>Demais Veiculos</t>
+  </si>
+  <si>
+    <t>PMEs</t>
+  </si>
+  <si>
+    <t>Large Corporate</t>
+  </si>
+  <si>
+    <t>Originacao de Financiamentos de Veiculos</t>
+  </si>
+  <si>
+    <t>Médias</t>
+  </si>
+  <si>
+    <t>Leves Usados</t>
+  </si>
+  <si>
+    <t>Depositos Interfinanceiros</t>
+  </si>
+  <si>
+    <t>Empréstimos e Repasses</t>
+  </si>
+  <si>
+    <t>Depositos a Prazo</t>
+  </si>
+  <si>
+    <t>Instrumentos de Capital</t>
+  </si>
+  <si>
+    <t>Cessões de Crédito</t>
+  </si>
+  <si>
+    <t>FIDC</t>
+  </si>
+  <si>
+    <t>Titulos Emitidos no Exterior</t>
+  </si>
+  <si>
+    <t>Letras Financeiras</t>
+  </si>
+  <si>
+    <t>Nivel II</t>
+  </si>
+  <si>
+    <t>Nivel I Complementar</t>
+  </si>
+  <si>
+    <t>Nivel I Principal</t>
+  </si>
+  <si>
+    <t>Indice Basileia</t>
+  </si>
+  <si>
+    <t>3T25 vs 2t</t>
+  </si>
+  <si>
+    <t>Capital 2T25</t>
+  </si>
+  <si>
+    <t>Lucro Liquido JCP</t>
+  </si>
+  <si>
+    <t>Nivel 1 Compl.</t>
+  </si>
+  <si>
+    <t>Ajustes Prud</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Outros Veiculos</t>
+  </si>
+  <si>
+    <t>Premios de Seguros</t>
+  </si>
+  <si>
+    <t>CIB</t>
+  </si>
+  <si>
+    <t>CORPORATE</t>
+  </si>
+  <si>
+    <t>LARGE + if</t>
+  </si>
+  <si>
+    <t>Exposicao de Carteira Do atacado</t>
+  </si>
+  <si>
+    <t>Agroindustria</t>
+  </si>
+  <si>
+    <t>Inst. Financeiras</t>
+  </si>
+  <si>
+    <t>Industria</t>
+  </si>
+  <si>
+    <t>Servicos</t>
+  </si>
+  <si>
+    <t>Acucar e Etanol</t>
+  </si>
+  <si>
+    <t>Construcao Civil</t>
+  </si>
+  <si>
+    <t>Telecomunicacoes</t>
+  </si>
+  <si>
+    <t>Cooperativas</t>
+  </si>
+  <si>
+    <t>Oleo e Gas</t>
+  </si>
+  <si>
+    <t>Project Finance</t>
+  </si>
+  <si>
+    <t>Montadoras</t>
+  </si>
+  <si>
+    <t>Mineracao</t>
+  </si>
+  <si>
+    <t>Energia Eletrica</t>
+  </si>
+  <si>
+    <t>Locadoras</t>
+  </si>
+  <si>
+    <t>Saude</t>
+  </si>
+  <si>
+    <t>Saneamento</t>
+  </si>
+  <si>
+    <t>Farmaceutico</t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
+  <si>
+    <t>4T25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -254,7 +480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -265,6 +491,16 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,6 +1005,841 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
+  <dimension ref="A3:N5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4">
+        <v>5.5</v>
+      </c>
+      <c r="C4">
+        <v>6.7</v>
+      </c>
+      <c r="D4">
+        <v>7.2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4">
+        <v>441.7</v>
+      </c>
+      <c r="K4">
+        <v>314.2</v>
+      </c>
+      <c r="L4">
+        <v>354.2</v>
+      </c>
+      <c r="M4">
+        <v>1252.4000000000001</v>
+      </c>
+      <c r="N4">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5">
+        <v>45.6</v>
+      </c>
+      <c r="C5">
+        <v>44.7</v>
+      </c>
+      <c r="D5">
+        <v>44.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="G1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C3">
+        <v>2.5</v>
+      </c>
+      <c r="D3">
+        <v>2.8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>13.2</v>
+      </c>
+      <c r="C4">
+        <v>13.6</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5">
+        <v>10.5</v>
+      </c>
+      <c r="C5">
+        <v>9.9</v>
+      </c>
+      <c r="D5">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22">
+        <v>13</v>
+      </c>
+      <c r="I22">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
+  <dimension ref="B7:P10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>5.6</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>4.2</v>
+      </c>
+      <c r="G7">
+        <v>4.5</v>
+      </c>
+      <c r="H7">
+        <v>3.5</v>
+      </c>
+      <c r="I7">
+        <v>3.7</v>
+      </c>
+      <c r="J7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K7">
+        <v>5.3</v>
+      </c>
+      <c r="L7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N7">
+        <v>4.3</v>
+      </c>
+      <c r="O7">
+        <v>4.8</v>
+      </c>
+      <c r="P7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>5.5</v>
+      </c>
+      <c r="E8">
+        <v>4.7</v>
+      </c>
+      <c r="F8">
+        <v>4.8</v>
+      </c>
+      <c r="G8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H8">
+        <v>4.3</v>
+      </c>
+      <c r="I8">
+        <v>4.7</v>
+      </c>
+      <c r="J8">
+        <v>6.2</v>
+      </c>
+      <c r="K8">
+        <v>6.4</v>
+      </c>
+      <c r="L8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M8">
+        <v>5.2</v>
+      </c>
+      <c r="N8">
+        <v>5.5</v>
+      </c>
+      <c r="O8">
+        <v>6.1</v>
+      </c>
+      <c r="P8">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E9">
+        <v>4.2</v>
+      </c>
+      <c r="F9">
+        <v>4.3</v>
+      </c>
+      <c r="G9">
+        <v>4.2</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>5.6</v>
+      </c>
+      <c r="E10">
+        <v>1.8</v>
+      </c>
+      <c r="F10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G10">
+        <v>2.8</v>
+      </c>
+      <c r="H10">
+        <v>0.5</v>
+      </c>
+      <c r="I10">
+        <v>0.1</v>
+      </c>
+      <c r="J10">
+        <v>0.2</v>
+      </c>
+      <c r="K10">
+        <v>0.4</v>
+      </c>
+      <c r="L10">
+        <v>0.6</v>
+      </c>
+      <c r="M10">
+        <v>0.4</v>
+      </c>
+      <c r="N10">
+        <v>0.3</v>
+      </c>
+      <c r="O10">
+        <v>0.5</v>
+      </c>
+      <c r="P10">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
+  <dimension ref="C4:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F5">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.223</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-0.33400000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>4.2649999999999997</v>
+      </c>
+      <c r="E6">
+        <v>3.9140000000000001</v>
+      </c>
+      <c r="F6">
+        <v>3.7949999999999999</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-0.03</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E7">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="F7">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-0.13600000000000001</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-0.248</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>3.83</v>
+      </c>
+      <c r="E8">
+        <v>4.5119999999999996</v>
+      </c>
+      <c r="F8">
+        <v>4.7969999999999997</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6.3E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>8.76</v>
+      </c>
+      <c r="E9">
+        <v>9.0030000000000001</v>
+      </c>
+      <c r="F9">
+        <v>9.08</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="3">
+        <v>-0.154</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-0.26600000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
+  <dimension ref="C14:F15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>4.5419999999999998</v>
+      </c>
+      <c r="E15">
+        <v>4.8109999999999999</v>
+      </c>
+      <c r="F15">
+        <v>4.8289999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
+  <dimension ref="W3:AK9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="23:37" x14ac:dyDescent="0.25">
+      <c r="W3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="23:37" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <v>9.9</v>
+      </c>
+      <c r="X9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Y9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Z9">
+        <v>9.6</v>
+      </c>
+      <c r="AA9">
+        <v>9.9</v>
+      </c>
+      <c r="AB9">
+        <v>11.1</v>
+      </c>
+      <c r="AC9">
+        <v>9.9</v>
+      </c>
+      <c r="AD9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AE9">
+        <v>9.5</v>
+      </c>
+      <c r="AJ9">
+        <v>9.6</v>
+      </c>
+      <c r="AK9">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44452379-0FE0-41DB-BDE4-79B6F1D7D785}">
   <dimension ref="A1:N285"/>
@@ -2629,196 +3700,240 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
-  <dimension ref="B7:P10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23508980-3939-4D95-9A4C-23A64D6BD062}">
+  <dimension ref="C3:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>5.6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>4.2</v>
-      </c>
-      <c r="G7">
-        <v>4.5</v>
-      </c>
-      <c r="H7">
-        <v>3.5</v>
-      </c>
-      <c r="I7">
-        <v>3.7</v>
-      </c>
-      <c r="J7">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K7">
-        <v>5.3</v>
-      </c>
-      <c r="L7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N7">
-        <v>4.3</v>
-      </c>
-      <c r="O7">
-        <v>4.8</v>
-      </c>
-      <c r="P7">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>5.5</v>
-      </c>
-      <c r="E8">
-        <v>4.7</v>
-      </c>
-      <c r="F8">
-        <v>4.8</v>
-      </c>
-      <c r="G8">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H8">
-        <v>4.3</v>
-      </c>
-      <c r="I8">
-        <v>4.7</v>
-      </c>
-      <c r="J8">
-        <v>6.2</v>
-      </c>
-      <c r="K8">
-        <v>6.4</v>
-      </c>
-      <c r="L8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M8">
-        <v>5.2</v>
-      </c>
-      <c r="N8">
-        <v>5.5</v>
-      </c>
-      <c r="O8">
-        <v>6.1</v>
-      </c>
-      <c r="P8">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>2.9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E9">
-        <v>4.2</v>
-      </c>
-      <c r="F9">
-        <v>4.3</v>
-      </c>
-      <c r="G9">
-        <v>4.2</v>
-      </c>
-      <c r="H9">
-        <v>3.6</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
-      </c>
-      <c r="J9">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K9">
+      <c r="D10">
+        <v>2372</v>
+      </c>
+      <c r="E10">
+        <v>685</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>6782</v>
+      </c>
+      <c r="I10">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>2311</v>
+      </c>
+      <c r="E11">
+        <v>556</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <v>6976</v>
+      </c>
+      <c r="I11">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>2295</v>
+      </c>
+      <c r="E12">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="L9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N9">
+      <c r="D18">
+        <v>284</v>
+      </c>
+      <c r="E18">
+        <v>2088</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>796</v>
+      </c>
+      <c r="I18">
+        <v>5986</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>232</v>
+      </c>
+      <c r="E19">
+        <v>2079</v>
+      </c>
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>793</v>
+      </c>
+      <c r="I19">
+        <v>6183</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>244</v>
+      </c>
+      <c r="E20">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
         <v>5</v>
       </c>
-      <c r="O9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>5.6</v>
-      </c>
-      <c r="E10">
-        <v>1.8</v>
-      </c>
-      <c r="F10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G10">
-        <v>2.8</v>
-      </c>
-      <c r="H10">
-        <v>0.5</v>
-      </c>
-      <c r="I10">
-        <v>0.1</v>
-      </c>
-      <c r="J10">
-        <v>0.2</v>
-      </c>
-      <c r="K10">
-        <v>0.4</v>
-      </c>
-      <c r="L10">
-        <v>0.6</v>
-      </c>
-      <c r="M10">
-        <v>0.4</v>
-      </c>
-      <c r="N10">
-        <v>0.3</v>
-      </c>
-      <c r="O10">
-        <v>0.5</v>
-      </c>
-      <c r="P10">
-        <v>0.8</v>
+      <c r="D25">
+        <v>241</v>
+      </c>
+      <c r="E25">
+        <v>444</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25">
+        <v>693</v>
+      </c>
+      <c r="I25">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>165</v>
+      </c>
+      <c r="E26">
+        <v>391</v>
+      </c>
+      <c r="G26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26">
+        <v>585</v>
+      </c>
+      <c r="I26">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>205</v>
+      </c>
+      <c r="E27">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -2827,136 +3942,426 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
-  <dimension ref="C4:H10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FAFF65-4D1E-443F-BDF3-D7DA42FEA733}">
+  <dimension ref="B2:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="K2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>19</v>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="K4" s="9">
+        <v>1.72</v>
+      </c>
+      <c r="L4" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="M4" s="9">
+        <v>2.21</v>
+      </c>
+      <c r="N4" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="O4" s="9">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>1159</v>
+      </c>
+      <c r="D6">
+        <v>1167</v>
+      </c>
+      <c r="E6">
+        <v>972</v>
+      </c>
+      <c r="F6">
+        <v>3275</v>
+      </c>
+      <c r="G6">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7">
+        <v>-155</v>
+      </c>
+      <c r="D7">
+        <v>-243</v>
+      </c>
+      <c r="E7">
+        <v>-92</v>
+      </c>
+      <c r="F7">
+        <v>-458</v>
+      </c>
+      <c r="G7">
+        <v>-501</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="K2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B33BFE8-86C2-496F-B733-78BC5607B7C2}">
+  <dimension ref="B2:O6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="J2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="12">
+        <v>472</v>
+      </c>
+      <c r="D4" s="12">
+        <v>450</v>
+      </c>
+      <c r="E4" s="12">
+        <v>494</v>
+      </c>
+      <c r="F4" s="12">
+        <v>1317</v>
+      </c>
+      <c r="G4" s="12">
+        <v>1411</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.377</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.379</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.373</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.373</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>349</v>
       </c>
       <c r="D5">
-        <v>0.13900000000000001</v>
+        <v>346</v>
       </c>
       <c r="E5">
-        <v>0.11899999999999999</v>
+        <v>311</v>
       </c>
       <c r="F5">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.223</v>
-      </c>
-      <c r="H5" s="3">
-        <v>-0.33400000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>20</v>
+        <v>981</v>
+      </c>
+      <c r="G5">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6">
+        <v>102</v>
       </c>
       <c r="D6">
-        <v>4.2649999999999997</v>
+        <v>110</v>
       </c>
       <c r="E6">
-        <v>3.9140000000000001</v>
+        <v>113</v>
       </c>
       <c r="F6">
-        <v>3.7949999999999999</v>
-      </c>
-      <c r="G6" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="H6" s="3">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>21</v>
+        <v>309</v>
+      </c>
+      <c r="G6">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
+  <dimension ref="B3:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.7</v>
+      </c>
+      <c r="D4">
+        <v>0.6</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>4.8</v>
+      </c>
+      <c r="E5">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>3.8</v>
+      </c>
+      <c r="D6">
+        <v>4.5</v>
+      </c>
+      <c r="E6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>4.3</v>
       </c>
       <c r="D7">
-        <v>0.52500000000000002</v>
+        <v>3.9</v>
       </c>
       <c r="E7">
-        <v>0.45700000000000002</v>
-      </c>
-      <c r="F7">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="G7" s="3">
-        <v>-0.13600000000000001</v>
-      </c>
-      <c r="H7" s="3">
-        <v>-0.248</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>22</v>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>3.83</v>
+        <v>6.7</v>
       </c>
       <c r="E8">
-        <v>4.5119999999999996</v>
-      </c>
-      <c r="F8">
-        <v>4.7969999999999997</v>
-      </c>
-      <c r="G8" s="3">
-        <v>6.3E-2</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.253</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>15</v>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>45.6</v>
       </c>
       <c r="D9">
-        <v>8.76</v>
+        <v>44.7</v>
       </c>
       <c r="E9">
-        <v>9.0030000000000001</v>
-      </c>
-      <c r="F9">
-        <v>9.08</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="G10" s="3">
-        <v>-0.154</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-0.26600000000000001</v>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D10">
+        <v>2.5</v>
+      </c>
+      <c r="E10">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>23.7</v>
+      </c>
+      <c r="D11">
+        <v>23.5</v>
+      </c>
+      <c r="E11">
+        <v>23.9</v>
       </c>
     </row>
   </sheetData>
@@ -2964,37 +4369,257 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
-  <dimension ref="C14:F15"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
+  <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="J4" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="E14" t="s">
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F6" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="G6" s="11">
+        <v>3</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="13">
+        <v>6.4</v>
+      </c>
+      <c r="D7" s="13">
+        <v>4.7</v>
+      </c>
+      <c r="E7" s="13">
+        <v>5.4</v>
+      </c>
+      <c r="F7" s="13">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="G7" s="13">
         <v>15</v>
       </c>
-      <c r="D15">
-        <v>4.5419999999999998</v>
-      </c>
-      <c r="E15">
-        <v>4.8109999999999999</v>
-      </c>
-      <c r="F15">
-        <v>4.8289999999999997</v>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="J4:O4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <v>5.5</v>
+      </c>
+      <c r="D3">
+        <v>1.3</v>
+      </c>
+      <c r="E3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>6.5</v>
+      </c>
+      <c r="D4">
+        <v>5.3</v>
+      </c>
+      <c r="E4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>37.1</v>
+      </c>
+      <c r="D5">
+        <v>28.4</v>
+      </c>
+      <c r="E5">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>3.2</v>
+      </c>
+      <c r="D6">
+        <v>3.4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7">
+        <v>10.4</v>
+      </c>
+      <c r="D7">
+        <v>6.8</v>
+      </c>
+      <c r="E7">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>0.7</v>
+      </c>
+      <c r="D8">
+        <v>0.8</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>4.2</v>
+      </c>
+      <c r="D9">
+        <v>7.2</v>
+      </c>
+      <c r="E9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10">
+        <v>35</v>
+      </c>
+      <c r="D10">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E10">
+        <v>41.9</v>
       </c>
     </row>
   </sheetData>
@@ -3002,82 +4627,151 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
-  <dimension ref="W3:AK9"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
+  <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="23:37" x14ac:dyDescent="0.25">
-      <c r="W3" t="s">
-        <v>1</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="s">
+    <row r="2" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="23:37" x14ac:dyDescent="0.25">
-      <c r="W9">
-        <v>9.9</v>
-      </c>
-      <c r="X9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="Y9">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="Z9">
-        <v>9.6</v>
-      </c>
-      <c r="AA9">
-        <v>9.9</v>
-      </c>
-      <c r="AB9">
-        <v>11.1</v>
-      </c>
-      <c r="AC9">
-        <v>9.9</v>
-      </c>
-      <c r="AD9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AE9">
-        <v>9.5</v>
-      </c>
-      <c r="AJ9">
-        <v>9.6</v>
-      </c>
-      <c r="AK9">
-        <v>9.6999999999999993</v>
-      </c>
+      <c r="K3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.129</v>
+      </c>
+      <c r="J6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="7" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J2:M2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/testing.xlsx
+++ b/testing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\ppt-doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4750BD56-567F-4998-9B34-817586B54504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9697AFE-67AF-4EF7-86F2-C22B8F53708D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33615" yWindow="1725" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="10" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="5" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,17 @@
     <sheet name="slide_8" sheetId="7" r:id="rId3"/>
     <sheet name="slide_9" sheetId="8" r:id="rId4"/>
     <sheet name="slide_11" sheetId="9" r:id="rId5"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId6"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId7"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId8"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId9"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId10"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId11"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId12"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId13"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId14"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId15"/>
+    <sheet name="Carteira" sheetId="16" r:id="rId6"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId7"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId8"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId9"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId10"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId11"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId12"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId13"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId14"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId15"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="137">
   <si>
     <t>Labels</t>
   </si>
@@ -419,6 +420,51 @@
   </si>
   <si>
     <t>4T25</t>
+  </si>
+  <si>
+    <t>Veiculos Pesados</t>
+  </si>
+  <si>
+    <t>Motos e Veiculos Novos</t>
+  </si>
+  <si>
+    <t>Outros (FGTS + Saúde)</t>
+  </si>
+  <si>
+    <t>segmento varejo</t>
+  </si>
+  <si>
+    <t>Varejo - Produtos de Entrada</t>
+  </si>
+  <si>
+    <t>Varelo Relacional</t>
+  </si>
+  <si>
+    <t>Empréstimo com Garantia Vericular (EGV)</t>
+  </si>
+  <si>
+    <t>Cartão de Crédito</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Segmento Atacado</t>
+  </si>
+  <si>
+    <t>Large Corporate + Instituições Financeiras</t>
+  </si>
+  <si>
+    <t>Pequenas e Médias Empresas</t>
+  </si>
+  <si>
+    <t>Segmento Atacado Ampliado</t>
+  </si>
+  <si>
+    <t>Avais e Fianças Prestados</t>
+  </si>
+  <si>
+    <t>TVM privado</t>
   </si>
 </sst>
 </file>
@@ -427,9 +473,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,6 +504,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -480,7 +534,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -495,16 +549,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1006,6 +1061,155 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
+  <dimension ref="D2:O7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+    </row>
+    <row r="3" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.129</v>
+      </c>
+      <c r="J6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="7" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1090,17 +1294,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="G1" t="s">
         <v>102</v>
       </c>
@@ -1386,7 +1590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1584,7 +1788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C4:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1722,7 +1926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
   <dimension ref="C14:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1760,7 +1964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3950,22 +4154,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="K2" s="10" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="K2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
@@ -4097,22 +4301,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="J2" s="10" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="J2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
@@ -4150,19 +4354,19 @@
       <c r="B4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>472</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>450</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>494</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>1317</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>1411</v>
       </c>
       <c r="J4" s="8" t="s">
@@ -4234,6 +4438,302 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790767E-187D-4BED-BBAB-0D1EEC80F334}">
+  <dimension ref="C12:N36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="14">
+        <v>61464</v>
+      </c>
+      <c r="E14" s="14">
+        <v>65935</v>
+      </c>
+      <c r="F14" s="14">
+        <v>69333</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="14">
+        <v>52789</v>
+      </c>
+      <c r="E15" s="14">
+        <v>56267</v>
+      </c>
+      <c r="F15" s="14">
+        <v>58802</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16">
+        <v>42236</v>
+      </c>
+      <c r="E16">
+        <v>44852</v>
+      </c>
+      <c r="F16">
+        <v>46888</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17">
+        <v>2219</v>
+      </c>
+      <c r="E17">
+        <v>2913</v>
+      </c>
+      <c r="F17">
+        <v>3258</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18">
+        <v>3548</v>
+      </c>
+      <c r="E18">
+        <v>4262</v>
+      </c>
+      <c r="F18">
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19">
+        <v>4167</v>
+      </c>
+      <c r="E19">
+        <v>3795</v>
+      </c>
+      <c r="F19">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
+        <v>513</v>
+      </c>
+      <c r="E20">
+        <v>395</v>
+      </c>
+      <c r="F20">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21">
+        <v>106</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="14">
+        <v>8857</v>
+      </c>
+      <c r="E22" s="14">
+        <v>9668</v>
+      </c>
+      <c r="F22" s="14">
+        <v>10531</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23">
+        <v>4032</v>
+      </c>
+      <c r="E23">
+        <v>4797</v>
+      </c>
+      <c r="F23">
+        <v>5262</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24">
+        <v>4765</v>
+      </c>
+      <c r="E24">
+        <v>4829</v>
+      </c>
+      <c r="F24">
+        <v>5230</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>43</v>
+      </c>
+      <c r="F25">
+        <v>39</v>
+      </c>
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="3:14" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C27" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="14">
+        <v>12884</v>
+      </c>
+      <c r="E27" s="14">
+        <v>9628</v>
+      </c>
+      <c r="F27" s="14">
+        <v>10318</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>6426</v>
+      </c>
+      <c r="E28">
+        <v>5949</v>
+      </c>
+      <c r="F28">
+        <v>6547</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29">
+        <v>5114</v>
+      </c>
+      <c r="E29">
+        <v>2655</v>
+      </c>
+      <c r="F29">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30">
+        <v>1343</v>
+      </c>
+      <c r="E30">
+        <v>1025</v>
+      </c>
+      <c r="F30">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C34" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="14">
+        <v>28856</v>
+      </c>
+      <c r="E34" s="14">
+        <v>26665</v>
+      </c>
+      <c r="F34" s="14">
+        <v>28323</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35">
+        <v>6008</v>
+      </c>
+      <c r="E35">
+        <v>5934</v>
+      </c>
+      <c r="F35">
+        <v>6120</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36">
+        <v>9964</v>
+      </c>
+      <c r="E36">
+        <v>11103</v>
+      </c>
+      <c r="F36">
+        <v>11885</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
   <dimension ref="B3:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4369,28 +4869,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
   <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="J4" s="10" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="J4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
@@ -4428,19 +4928,19 @@
       <c r="B6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>0.9</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>3.1</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>3</v>
       </c>
       <c r="J6" s="8" t="s">
@@ -4466,19 +4966,19 @@
       <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>6.4</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>4.7</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>5.4</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>18.100000000000001</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>15</v>
       </c>
     </row>
@@ -4491,7 +4991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4625,153 +5125,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
-  <dimension ref="D2:O7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-    </row>
-    <row r="3" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1.4E-2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>2.4E-2</v>
-      </c>
-      <c r="J5" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3">
-        <v>2.4E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.13</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.127</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.129</v>
-      </c>
-      <c r="J6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.127</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3">
-        <v>0.129</v>
-      </c>
-    </row>
-    <row r="7" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,27 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9697AFE-67AF-4EF7-86F2-C22B8F53708D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071CF139-2C15-49A9-81E8-22D83EEBF4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="5" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="1875" yWindow="1425" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
-    <sheet name="DRE Saida" sheetId="1" r:id="rId1"/>
-    <sheet name="Pizza Teste" sheetId="6" r:id="rId2"/>
-    <sheet name="slide_8" sheetId="7" r:id="rId3"/>
-    <sheet name="slide_9" sheetId="8" r:id="rId4"/>
-    <sheet name="slide_11" sheetId="9" r:id="rId5"/>
-    <sheet name="Carteira" sheetId="16" r:id="rId6"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId7"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId8"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId9"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId10"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId11"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId12"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId13"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId14"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId15"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId16"/>
+    <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
+    <sheet name="Tabelas" sheetId="19" r:id="rId2"/>
+    <sheet name="DRE Saida" sheetId="1" r:id="rId3"/>
+    <sheet name="Pizza Teste" sheetId="6" r:id="rId4"/>
+    <sheet name="slide_8" sheetId="7" r:id="rId5"/>
+    <sheet name="slide_9" sheetId="8" r:id="rId6"/>
+    <sheet name="slide_11" sheetId="9" r:id="rId7"/>
+    <sheet name="Carteira" sheetId="16" r:id="rId8"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId9"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId10"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId11"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId12"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId13"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId14"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId15"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId16"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId17"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="143">
   <si>
     <t>Labels</t>
   </si>
@@ -465,6 +467,24 @@
   </si>
   <si>
     <t>TVM privado</t>
+  </si>
+  <si>
+    <t>Receita de Prestação de Serviços e Corretagem</t>
+  </si>
+  <si>
+    <t>Margem Financeira Com Clientes</t>
+  </si>
+  <si>
+    <t>Margem Financeira com Mercado</t>
+  </si>
+  <si>
+    <t>Receitas de Corretagem e Seguro</t>
+  </si>
+  <si>
+    <t>Receitas de Prestação de Servicos e Corretagem</t>
+  </si>
+  <si>
+    <t>Receitas de Prestação de Serviços (exclui corretagem de seguros)</t>
   </si>
 </sst>
 </file>
@@ -534,7 +554,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -556,6 +576,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,169 +911,167 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417E299C-E79D-4FD4-B55D-DB1E7B3327CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D0A736-06AB-48E7-AFFE-0EC2903148F5}">
   <dimension ref="B3:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="42.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>285</v>
-      </c>
-      <c r="D18">
-        <v>302</v>
-      </c>
-      <c r="E18">
-        <v>321</v>
-      </c>
-      <c r="F18">
-        <v>363</v>
-      </c>
-      <c r="G18">
-        <v>496</v>
-      </c>
-      <c r="H18">
-        <v>542</v>
-      </c>
-      <c r="I18">
-        <v>480</v>
-      </c>
-      <c r="J18">
-        <v>459</v>
-      </c>
-      <c r="K18">
-        <v>461</v>
-      </c>
-      <c r="L18">
-        <v>1180</v>
-      </c>
-      <c r="M18">
-        <v>1400</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="G3">
+        <v>2024</v>
+      </c>
+      <c r="H3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>3214</v>
+      </c>
+      <c r="E4">
+        <v>2919</v>
+      </c>
+      <c r="F4">
+        <v>3136</v>
+      </c>
+      <c r="G4">
+        <v>11980</v>
+      </c>
+      <c r="H4">
+        <v>11913</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5">
+        <v>2519</v>
+      </c>
+      <c r="E5">
+        <v>2295</v>
+      </c>
+      <c r="F5">
+        <v>2304</v>
+      </c>
+      <c r="G5">
+        <v>9301</v>
+      </c>
+      <c r="H5">
+        <v>9283</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6">
+        <v>2367</v>
+      </c>
+      <c r="E6">
+        <v>2051</v>
+      </c>
+      <c r="F6">
+        <v>2131</v>
+      </c>
+      <c r="G6">
+        <v>8353</v>
+      </c>
+      <c r="H6">
+        <v>8317</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7">
+        <v>152</v>
+      </c>
+      <c r="E7">
+        <v>244</v>
+      </c>
+      <c r="F7">
+        <v>172</v>
+      </c>
+      <c r="G7">
+        <v>947</v>
+      </c>
+      <c r="H7">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9">
+        <v>695</v>
+      </c>
+      <c r="E9">
+        <v>624</v>
+      </c>
+      <c r="F9">
+        <v>832</v>
+      </c>
+      <c r="G9">
+        <v>2679</v>
+      </c>
+      <c r="H9">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="N18" s="1"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="L21" s="1"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="4">
-        <v>0.09</v>
-      </c>
-      <c r="D25" s="5">
-        <v>9.4E-2</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0.111</v>
-      </c>
-      <c r="G25" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="H25" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="I25" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="J25" s="5">
-        <v>0.151</v>
-      </c>
-      <c r="K25" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="L25" s="5">
-        <v>0.121</v>
-      </c>
-      <c r="M25" s="5">
-        <v>0.154</v>
-      </c>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B35" s="2"/>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B36" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1061,6 +1080,264 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
+  <dimension ref="B4:O7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="J4" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F6" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="G6" s="10">
+        <v>3</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="D7" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="E7" s="12">
+        <v>5.4</v>
+      </c>
+      <c r="F7" s="12">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="G7" s="12">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="J4:O4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <v>5.5</v>
+      </c>
+      <c r="D3">
+        <v>1.3</v>
+      </c>
+      <c r="E3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>6.5</v>
+      </c>
+      <c r="D4">
+        <v>5.3</v>
+      </c>
+      <c r="E4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>37.1</v>
+      </c>
+      <c r="D5">
+        <v>28.4</v>
+      </c>
+      <c r="E5">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>3.2</v>
+      </c>
+      <c r="D6">
+        <v>3.4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7">
+        <v>10.4</v>
+      </c>
+      <c r="D7">
+        <v>6.8</v>
+      </c>
+      <c r="E7">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>0.7</v>
+      </c>
+      <c r="D8">
+        <v>0.8</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>4.2</v>
+      </c>
+      <c r="D9">
+        <v>7.2</v>
+      </c>
+      <c r="E9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10">
+        <v>35</v>
+      </c>
+      <c r="D10">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E10">
+        <v>41.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
   <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1209,7 +1486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1294,7 +1571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1590,7 +1867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1788,7 +2065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C4:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1926,7 +2203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
   <dimension ref="C14:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1964,7 +2241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2045,6 +2322,273 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2DB3A40-3823-4B44-8654-968315449624}">
+  <dimension ref="C16:H31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="59.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="16" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16">
+        <v>2024</v>
+      </c>
+      <c r="H16">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="15"/>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19">
+        <v>239</v>
+      </c>
+      <c r="E19">
+        <v>205</v>
+      </c>
+      <c r="F19">
+        <v>290</v>
+      </c>
+      <c r="G19">
+        <v>932</v>
+      </c>
+      <c r="H19">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26">
+        <v>695</v>
+      </c>
+      <c r="E26">
+        <v>624</v>
+      </c>
+      <c r="F26">
+        <v>832</v>
+      </c>
+      <c r="G26">
+        <v>2679</v>
+      </c>
+      <c r="H26">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28">
+        <v>457</v>
+      </c>
+      <c r="E28">
+        <v>419</v>
+      </c>
+      <c r="F28">
+        <v>542</v>
+      </c>
+      <c r="G28">
+        <v>1748</v>
+      </c>
+      <c r="H28">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="F31" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417E299C-E79D-4FD4-B55D-DB1E7B3327CE}">
+  <dimension ref="B3:N36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>285</v>
+      </c>
+      <c r="D18">
+        <v>302</v>
+      </c>
+      <c r="E18">
+        <v>321</v>
+      </c>
+      <c r="F18">
+        <v>363</v>
+      </c>
+      <c r="G18">
+        <v>496</v>
+      </c>
+      <c r="H18">
+        <v>542</v>
+      </c>
+      <c r="I18">
+        <v>480</v>
+      </c>
+      <c r="J18">
+        <v>459</v>
+      </c>
+      <c r="K18">
+        <v>461</v>
+      </c>
+      <c r="L18">
+        <v>1180</v>
+      </c>
+      <c r="M18">
+        <v>1400</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L21" s="1"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C25" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="D25" s="5">
+        <v>9.4E-2</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.111</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0.151</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0.121</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44452379-0FE0-41DB-BDE4-79B6F1D7D785}">
   <dimension ref="A1:N285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3903,7 +4447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23508980-3939-4D95-9A4C-23A64D6BD062}">
   <dimension ref="C3:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4145,7 +4689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FAFF65-4D1E-443F-BDF3-D7DA42FEA733}">
   <dimension ref="B2:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4287,7 +4831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B33BFE8-86C2-496F-B733-78BC5607B7C2}">
   <dimension ref="B2:O6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4437,7 +4981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790767E-187D-4BED-BBAB-0D1EEC80F334}">
   <dimension ref="C12:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4733,7 +5277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
   <dimension ref="B3:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4867,262 +5411,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
-  <dimension ref="B4:O7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="J4" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F6" s="10">
-        <v>3.1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>3</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0.42</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="12">
-        <v>6.4</v>
-      </c>
-      <c r="D7" s="12">
-        <v>4.7</v>
-      </c>
-      <c r="E7" s="12">
-        <v>5.4</v>
-      </c>
-      <c r="F7" s="12">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="G7" s="12">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="J4:O4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
-  <dimension ref="B2:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3">
-        <v>5.5</v>
-      </c>
-      <c r="D3">
-        <v>1.3</v>
-      </c>
-      <c r="E3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4">
-        <v>6.5</v>
-      </c>
-      <c r="D4">
-        <v>5.3</v>
-      </c>
-      <c r="E4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5">
-        <v>37.1</v>
-      </c>
-      <c r="D5">
-        <v>28.4</v>
-      </c>
-      <c r="E5">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6">
-        <v>3.2</v>
-      </c>
-      <c r="D6">
-        <v>3.4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7">
-        <v>10.4</v>
-      </c>
-      <c r="D7">
-        <v>6.8</v>
-      </c>
-      <c r="E7">
-        <v>8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <v>0.7</v>
-      </c>
-      <c r="D8">
-        <v>0.8</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9">
-        <v>4.2</v>
-      </c>
-      <c r="D9">
-        <v>7.2</v>
-      </c>
-      <c r="E9">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10">
-        <v>35</v>
-      </c>
-      <c r="D10">
-        <v>40.799999999999997</v>
-      </c>
-      <c r="E10">
-        <v>41.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071CF139-2C15-49A9-81E8-22D83EEBF4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD23223-495C-44DB-A094-34FB20CB98F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="1425" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
     <sheet name="Tabelas" sheetId="19" r:id="rId2"/>
-    <sheet name="DRE Saida" sheetId="1" r:id="rId3"/>
-    <sheet name="Pizza Teste" sheetId="6" r:id="rId4"/>
-    <sheet name="slide_8" sheetId="7" r:id="rId5"/>
-    <sheet name="slide_9" sheetId="8" r:id="rId6"/>
-    <sheet name="slide_11" sheetId="9" r:id="rId7"/>
-    <sheet name="Carteira" sheetId="16" r:id="rId8"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId9"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId10"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId11"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId12"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId13"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId14"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId15"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId16"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId17"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId18"/>
+    <sheet name="Qualidade Cart 4966" sheetId="20" r:id="rId3"/>
+    <sheet name="DRE Saida" sheetId="1" r:id="rId4"/>
+    <sheet name="Pizza Teste" sheetId="6" r:id="rId5"/>
+    <sheet name="slide_8" sheetId="7" r:id="rId6"/>
+    <sheet name="slide_9" sheetId="8" r:id="rId7"/>
+    <sheet name="slide_11" sheetId="9" r:id="rId8"/>
+    <sheet name="Carteira" sheetId="16" r:id="rId9"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId10"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId11"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId12"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId13"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId14"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId15"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId16"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId17"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId18"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="145">
   <si>
     <t>Labels</t>
   </si>
@@ -485,6 +486,12 @@
   </si>
   <si>
     <t>Receitas de Prestação de Serviços (exclui corretagem de seguros)</t>
+  </si>
+  <si>
+    <t>Custo de Crédito</t>
+  </si>
+  <si>
+    <t>Recuperação de Crédito Baixados Como Prejuízo</t>
   </si>
 </sst>
 </file>
@@ -554,7 +561,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -572,11 +579,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1080,27 +1088,163 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
+  <dimension ref="B3:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.7</v>
+      </c>
+      <c r="D4">
+        <v>0.6</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>4.8</v>
+      </c>
+      <c r="E5">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>3.8</v>
+      </c>
+      <c r="D6">
+        <v>4.5</v>
+      </c>
+      <c r="E6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>4.3</v>
+      </c>
+      <c r="D7">
+        <v>3.9</v>
+      </c>
+      <c r="E7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+      <c r="D8">
+        <v>6.7</v>
+      </c>
+      <c r="E8">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>45.6</v>
+      </c>
+      <c r="D9">
+        <v>44.7</v>
+      </c>
+      <c r="E9">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D10">
+        <v>2.5</v>
+      </c>
+      <c r="E10">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>23.7</v>
+      </c>
+      <c r="D11">
+        <v>23.5</v>
+      </c>
+      <c r="E11">
+        <v>23.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
   <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="J4" s="13" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="J4" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
@@ -1201,7 +1345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1337,7 +1481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
   <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1355,12 +1499,12 @@
       <c r="E2" t="s">
         <v>90</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
     </row>
     <row r="3" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
@@ -1486,7 +1630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1571,17 +1715,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
       <c r="G1" t="s">
         <v>102</v>
       </c>
@@ -1867,7 +2011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2065,7 +2209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C4:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2203,7 +2347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
   <dimension ref="C14:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2241,7 +2385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2323,13 +2467,140 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2DB3A40-3823-4B44-8654-968315449624}">
-  <dimension ref="C16:H31"/>
+  <dimension ref="C2:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="59.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2">
+        <v>2024</v>
+      </c>
+      <c r="H2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5">
+        <v>187</v>
+      </c>
+      <c r="E5">
+        <v>92</v>
+      </c>
+      <c r="F5">
+        <v>201</v>
+      </c>
+      <c r="G5">
+        <v>645</v>
+      </c>
+      <c r="H5">
+        <v>702</v>
+      </c>
+      <c r="I5">
+        <v>118.2</v>
+      </c>
+      <c r="J5">
+        <v>7.5</v>
+      </c>
+      <c r="K5">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9">
+        <v>776</v>
+      </c>
+      <c r="E9">
+        <v>880</v>
+      </c>
+      <c r="F9">
+        <v>1029</v>
+      </c>
+      <c r="G9">
+        <v>3593</v>
+      </c>
+      <c r="H9">
+        <v>3698</v>
+      </c>
+      <c r="I9">
+        <v>16.8</v>
+      </c>
+      <c r="J9">
+        <v>32.6</v>
+      </c>
+      <c r="K9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>963</v>
+      </c>
+      <c r="E13">
+        <v>972</v>
+      </c>
+      <c r="F13">
+        <v>1230</v>
+      </c>
+      <c r="G13">
+        <v>4238</v>
+      </c>
+      <c r="H13">
+        <v>4400</v>
+      </c>
+      <c r="I13">
+        <v>26.5</v>
+      </c>
+      <c r="J13">
+        <v>27.7</v>
+      </c>
+      <c r="K13">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -2347,7 +2618,7 @@
       </c>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="15"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
@@ -2410,7 +2681,7 @@
       </c>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F31" s="15"/>
+      <c r="F31" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2418,6 +2689,38 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F8E16C-7218-4DFD-AF0C-6AD115ACF99C}">
+  <dimension ref="D2:F17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D17" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1.69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417E299C-E79D-4FD4-B55D-DB1E7B3327CE}">
   <dimension ref="B3:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2588,7 +2891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44452379-0FE0-41DB-BDE4-79B6F1D7D785}">
   <dimension ref="A1:N285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4447,7 +4750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23508980-3939-4D95-9A4C-23A64D6BD062}">
   <dimension ref="C3:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4689,7 +4992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FAFF65-4D1E-443F-BDF3-D7DA42FEA733}">
   <dimension ref="B2:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4698,22 +5001,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="K2" s="13" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="K2" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
@@ -4831,7 +5134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B33BFE8-86C2-496F-B733-78BC5607B7C2}">
   <dimension ref="B2:O6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4845,22 +5148,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="J2" s="13" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="J2" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
@@ -4981,7 +5284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790767E-187D-4BED-BBAB-0D1EEC80F334}">
   <dimension ref="C12:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5004,31 +5307,31 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="3:6" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="14" t="s">
+    <row r="14" spans="3:6" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>61464</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>65935</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <v>69333</v>
       </c>
     </row>
-    <row r="15" spans="3:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="14" t="s">
+    <row r="15" spans="3:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>52789</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>56267</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <v>58802</v>
       </c>
     </row>
@@ -5116,17 +5419,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="3:14" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="14" t="s">
+    <row r="22" spans="3:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>8857</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="13">
         <v>9668</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13">
         <v>10531</v>
       </c>
     </row>
@@ -5173,18 +5476,18 @@
       </c>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="3:14" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:14" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <v>12884</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="13">
         <v>9628</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <v>10318</v>
       </c>
     </row>
@@ -5231,16 +5534,16 @@
       </c>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="13">
         <v>28856</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="13">
         <v>26665</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="13">
         <v>28323</v>
       </c>
     </row>
@@ -5275,140 +5578,4 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
-  <dimension ref="B3:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4">
-        <v>0.7</v>
-      </c>
-      <c r="D4">
-        <v>0.6</v>
-      </c>
-      <c r="E4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-      <c r="D5">
-        <v>4.8</v>
-      </c>
-      <c r="E5">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>3.8</v>
-      </c>
-      <c r="D6">
-        <v>4.5</v>
-      </c>
-      <c r="E6">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7">
-        <v>4.3</v>
-      </c>
-      <c r="D7">
-        <v>3.9</v>
-      </c>
-      <c r="E7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-      <c r="D8">
-        <v>6.7</v>
-      </c>
-      <c r="E8">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9">
-        <v>45.6</v>
-      </c>
-      <c r="D9">
-        <v>44.7</v>
-      </c>
-      <c r="E9">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D10">
-        <v>2.5</v>
-      </c>
-      <c r="E10">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11">
-        <v>23.7</v>
-      </c>
-      <c r="D11">
-        <v>23.5</v>
-      </c>
-      <c r="E11">
-        <v>23.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD23223-495C-44DB-A094-34FB20CB98F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A92867D-2D7D-4570-88A6-E34AE727803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="3750" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
   <si>
     <t>Labels</t>
   </si>
@@ -492,6 +492,18 @@
   </si>
   <si>
     <t>Recuperação de Crédito Baixados Como Prejuízo</t>
+  </si>
+  <si>
+    <t>Total ADM + Pessoa</t>
+  </si>
+  <si>
+    <t>Depreciação e amortização</t>
+  </si>
+  <si>
+    <t>Despesas ADM (ex deprec)</t>
+  </si>
+  <si>
+    <t>Despesas de Pessoal</t>
   </si>
 </sst>
 </file>
@@ -561,7 +573,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -585,6 +597,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2013,7 +2026,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
-  <dimension ref="B7:P10"/>
+  <dimension ref="B7:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
@@ -2202,6 +2215,50 @@
       </c>
       <c r="P10">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C11" s="17">
+        <v>42339</v>
+      </c>
+      <c r="D11" s="17">
+        <v>42705</v>
+      </c>
+      <c r="E11" s="17">
+        <v>43070</v>
+      </c>
+      <c r="F11" s="17">
+        <v>43435</v>
+      </c>
+      <c r="G11" s="17">
+        <v>43800</v>
+      </c>
+      <c r="H11" s="17">
+        <v>44166</v>
+      </c>
+      <c r="I11" s="17">
+        <v>44531</v>
+      </c>
+      <c r="J11" s="17">
+        <v>44896</v>
+      </c>
+      <c r="K11" s="17">
+        <v>45261</v>
+      </c>
+      <c r="L11" s="17">
+        <v>45627</v>
+      </c>
+      <c r="M11" s="17">
+        <v>45717</v>
+      </c>
+      <c r="N11" s="17">
+        <v>45809</v>
+      </c>
+      <c r="O11" s="17">
+        <v>45901</v>
+      </c>
+      <c r="P11" s="17">
+        <v>45992</v>
       </c>
     </row>
   </sheetData>
@@ -2467,7 +2524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2DB3A40-3823-4B44-8654-968315449624}">
-  <dimension ref="C2:K31"/>
+  <dimension ref="C2:K47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="59.7109375" bestFit="1" customWidth="1"/>
@@ -2682,6 +2739,121 @@
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F31" s="14"/>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33">
+        <v>2024</v>
+      </c>
+      <c r="H33">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35">
+        <v>520</v>
+      </c>
+      <c r="E35">
+        <v>494</v>
+      </c>
+      <c r="F35">
+        <v>529</v>
+      </c>
+      <c r="G35">
+        <v>1837</v>
+      </c>
+      <c r="H35">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="39" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39">
+        <v>398</v>
+      </c>
+      <c r="E39">
+        <v>311</v>
+      </c>
+      <c r="F39">
+        <v>400</v>
+      </c>
+      <c r="G39">
+        <v>1379</v>
+      </c>
+      <c r="H39">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="45" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45">
+        <v>98</v>
+      </c>
+      <c r="E45">
+        <v>113</v>
+      </c>
+      <c r="F45">
+        <v>143</v>
+      </c>
+      <c r="G45">
+        <v>407</v>
+      </c>
+      <c r="H45">
+        <v>475</v>
+      </c>
+      <c r="I45">
+        <v>25.9</v>
+      </c>
+      <c r="J45">
+        <v>46.1</v>
+      </c>
+      <c r="K45">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="47" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>145</v>
+      </c>
+      <c r="D47">
+        <v>1015</v>
+      </c>
+      <c r="E47">
+        <v>919</v>
+      </c>
+      <c r="F47">
+        <v>1072</v>
+      </c>
+      <c r="G47">
+        <v>3623</v>
+      </c>
+      <c r="H47">
+        <v>2812</v>
+      </c>
+      <c r="I47">
+        <v>16.7</v>
+      </c>
+      <c r="J47">
+        <v>5.6</v>
+      </c>
+      <c r="K47">
+        <v>5.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A92867D-2D7D-4570-88A6-E34AE727803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BE5622-0DC3-48EA-A49D-D8CD5262B40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="3750" yWindow="1860" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="8" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="150">
   <si>
     <t>Labels</t>
   </si>
@@ -504,6 +504,9 @@
   </si>
   <si>
     <t>Despesas de Pessoal</t>
+  </si>
+  <si>
+    <t>Carteira de Crédito Ampliada</t>
   </si>
 </sst>
 </file>
@@ -5458,7 +5461,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790767E-187D-4BED-BBAB-0D1EEC80F334}">
-  <dimension ref="C12:N36"/>
+  <dimension ref="C12:N40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -5747,6 +5750,20 @@
         <v>11885</v>
       </c>
     </row>
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40">
+        <v>90502</v>
+      </c>
+      <c r="E40">
+        <v>92599</v>
+      </c>
+      <c r="F40">
+        <v>97656</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BE5622-0DC3-48EA-A49D-D8CD5262B40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E260031-EAE2-4F76-8436-EBDC11058235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="1860" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="8" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="1950" yWindow="1695" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="9" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -22,16 +22,17 @@
     <sheet name="slide_9" sheetId="8" r:id="rId7"/>
     <sheet name="slide_11" sheetId="9" r:id="rId8"/>
     <sheet name="Carteira" sheetId="16" r:id="rId9"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId10"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId11"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId12"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId13"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId14"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId15"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId16"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId17"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId18"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId19"/>
+    <sheet name="Veículos" sheetId="21" r:id="rId10"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId11"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId12"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId13"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId14"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId15"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId16"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId17"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId18"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId19"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="158">
   <si>
     <t>Labels</t>
   </si>
@@ -507,6 +508,30 @@
   </si>
   <si>
     <t>Carteira de Crédito Ampliada</t>
+  </si>
+  <si>
+    <t>corporate</t>
+  </si>
+  <si>
+    <t>large + if</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Taxa Média</t>
+  </si>
+  <si>
+    <t>Valor Entrada</t>
+  </si>
+  <si>
+    <t>Veiculos Uisados</t>
+  </si>
+  <si>
+    <t>Producao Veiculos Total</t>
+  </si>
+  <si>
+    <t>Prazo Médio</t>
   </si>
 </sst>
 </file>
@@ -596,11 +621,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1104,6 +1129,176 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231522F5-4F73-43C4-84CE-1220F786E75E}">
+  <dimension ref="C3:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3">
+        <v>2024</v>
+      </c>
+      <c r="H3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5">
+        <v>49</v>
+      </c>
+      <c r="E5">
+        <v>49</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="E6">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F6">
+        <v>39.5</v>
+      </c>
+      <c r="G6">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="H6">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7">
+        <v>85.8</v>
+      </c>
+      <c r="E7">
+        <v>83.1</v>
+      </c>
+      <c r="F7">
+        <v>84.2</v>
+      </c>
+      <c r="G7">
+        <v>85.8</v>
+      </c>
+      <c r="H7">
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8">
+        <v>7.1</v>
+      </c>
+      <c r="E8">
+        <v>6.5</v>
+      </c>
+      <c r="F8">
+        <v>8.1</v>
+      </c>
+      <c r="G8">
+        <v>28.3</v>
+      </c>
+      <c r="H8">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9">
+        <v>6.1260000000000003</v>
+      </c>
+      <c r="E9">
+        <v>5.4009999999999998</v>
+      </c>
+      <c r="F9">
+        <v>6.7850000000000001</v>
+      </c>
+      <c r="G9">
+        <v>24.265999999999998</v>
+      </c>
+      <c r="H9">
+        <v>21.97</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="E10">
+        <v>1.101</v>
+      </c>
+      <c r="F10">
+        <v>1.272</v>
+      </c>
+      <c r="G10">
+        <v>4.0049999999999999</v>
+      </c>
+      <c r="H10">
+        <v>4.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
   <dimension ref="B3:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1239,28 +1434,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
   <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="J4" s="15" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="J4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
@@ -1361,7 +1556,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1497,7 +1692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
   <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1515,12 +1710,12 @@
       <c r="E2" t="s">
         <v>90</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
@@ -1646,7 +1841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1731,17 +1926,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
       <c r="G1" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2221,46 +2416,46 @@
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>42339</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <v>42705</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>43070</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <v>43435</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>43800</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <v>44166</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="16">
         <v>44531</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <v>44896</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>45261</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="16">
         <v>45627</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="16">
         <v>45717</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="16">
         <v>45809</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="16">
         <v>45901</v>
       </c>
-      <c r="P11" s="17">
+      <c r="P11" s="16">
         <v>45992</v>
       </c>
     </row>
@@ -2269,7 +2464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C4:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2407,7 +2602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
   <dimension ref="C14:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2438,86 +2633,6 @@
       </c>
       <c r="F15">
         <v>4.8289999999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
-  <dimension ref="W3:AK9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="23:37" x14ac:dyDescent="0.25">
-      <c r="W3" t="s">
-        <v>1</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="23:37" x14ac:dyDescent="0.25">
-      <c r="W9">
-        <v>9.9</v>
-      </c>
-      <c r="X9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="Y9">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="Z9">
-        <v>9.6</v>
-      </c>
-      <c r="AA9">
-        <v>9.9</v>
-      </c>
-      <c r="AB9">
-        <v>11.1</v>
-      </c>
-      <c r="AC9">
-        <v>9.9</v>
-      </c>
-      <c r="AD9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AE9">
-        <v>9.5</v>
-      </c>
-      <c r="AJ9">
-        <v>9.6</v>
-      </c>
-      <c r="AK9">
-        <v>9.6999999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -2632,7 +2747,7 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="16"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D13">
@@ -2860,6 +2975,86 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
+  <dimension ref="W3:AK9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="23:37" x14ac:dyDescent="0.25">
+      <c r="W3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="23:37" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <v>9.9</v>
+      </c>
+      <c r="X9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Y9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Z9">
+        <v>9.6</v>
+      </c>
+      <c r="AA9">
+        <v>9.9</v>
+      </c>
+      <c r="AB9">
+        <v>11.1</v>
+      </c>
+      <c r="AC9">
+        <v>9.9</v>
+      </c>
+      <c r="AD9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AE9">
+        <v>9.5</v>
+      </c>
+      <c r="AJ9">
+        <v>9.6</v>
+      </c>
+      <c r="AK9">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5176,22 +5371,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="K2" s="15" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="K2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
@@ -5323,22 +5518,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="J2" s="15" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="J2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
@@ -5461,7 +5656,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790767E-187D-4BED-BBAB-0D1EEC80F334}">
-  <dimension ref="C12:N40"/>
+  <dimension ref="C12:N120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -5764,6 +5959,73 @@
         <v>97656</v>
       </c>
     </row>
+    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C117" t="s">
+        <v>150</v>
+      </c>
+      <c r="D117">
+        <v>14043</v>
+      </c>
+      <c r="E117">
+        <v>14016</v>
+      </c>
+      <c r="F117">
+        <v>15250</v>
+      </c>
+    </row>
+    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>151</v>
+      </c>
+      <c r="D118">
+        <v>11864</v>
+      </c>
+      <c r="E118">
+        <v>9844</v>
+      </c>
+      <c r="F118">
+        <v>9327</v>
+      </c>
+    </row>
+    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C119" t="s">
+        <v>41</v>
+      </c>
+      <c r="D119">
+        <v>2948</v>
+      </c>
+      <c r="E119">
+        <v>2805</v>
+      </c>
+      <c r="F119">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C120" t="s">
+        <v>152</v>
+      </c>
+      <c r="D120">
+        <v>28856</v>
+      </c>
+      <c r="E120">
+        <v>26665</v>
+      </c>
+      <c r="F120">
+        <v>28323</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E260031-EAE2-4F76-8436-EBDC11058235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199EDC08-794D-4DEF-9783-2A69E34A7932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1695" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="9" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="1965" yWindow="1695" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="9" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -1130,13 +1130,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231522F5-4F73-43C4-84CE-1220F786E75E}">
-  <dimension ref="C3:H10"/>
+  <dimension ref="C3:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>2</v>
       </c>
@@ -1153,143 +1153,144 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>153</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D5" s="3">
         <v>0.28799999999999998</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E5" s="3">
         <v>0.29099999999999998</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F5" s="3">
         <v>0.29099999999999998</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G5" s="3">
         <v>0.27</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H5" s="3">
         <v>0.29099999999999998</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>157</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>49</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>49</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>50</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>49</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>154</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>40.700000000000003</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>40.299999999999997</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>39.5</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>40.700000000000003</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <v>39.5</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>155</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>85.8</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>83.1</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>84.2</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>85.8</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>84.2</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>156</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>7.1</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>6.5</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>8.1</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>28.3</v>
       </c>
-      <c r="H8">
+      <c r="H9">
         <v>26.1</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>78</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>6.1260000000000003</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>5.4009999999999998</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>6.7850000000000001</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>24.265999999999998</v>
       </c>
-      <c r="H9">
+      <c r="H10">
         <v>21.97</v>
       </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>97</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>1.0109999999999999</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>1.101</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>1.272</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>4.0049999999999999</v>
       </c>
-      <c r="H10">
+      <c r="H11">
         <v>4.12</v>
       </c>
     </row>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199EDC08-794D-4DEF-9783-2A69E34A7932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C14D998-9646-4685-BCE0-71E2922D8C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="1695" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="9" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -23,16 +23,17 @@
     <sheet name="slide_11" sheetId="9" r:id="rId8"/>
     <sheet name="Carteira" sheetId="16" r:id="rId9"/>
     <sheet name="Veículos" sheetId="21" r:id="rId10"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId11"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId12"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId13"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId14"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId15"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId16"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId17"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId18"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId19"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId20"/>
+    <sheet name="Captações" sheetId="22" r:id="rId11"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId12"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId13"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId14"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId15"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId16"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId17"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId18"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId19"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId20"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="164">
   <si>
     <t>Labels</t>
   </si>
@@ -532,6 +533,24 @@
   </si>
   <si>
     <t>Prazo Médio</t>
+  </si>
+  <si>
+    <t>Depósitos a prazo</t>
+  </si>
+  <si>
+    <t>Títulos emitidos no exterior</t>
+  </si>
+  <si>
+    <t>cessões de crédito</t>
+  </si>
+  <si>
+    <t>empréstimos e repasses</t>
+  </si>
+  <si>
+    <t>depósitos interfinanceiros</t>
+  </si>
+  <si>
+    <t>instrumentos de capital</t>
   </si>
 </sst>
 </file>
@@ -1300,6 +1319,142 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088EF8FE-482E-42AC-8EA5-92878DC598D2}">
+  <dimension ref="B3:E15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5">
+        <v>35.5</v>
+      </c>
+      <c r="D5">
+        <v>41.9</v>
+      </c>
+      <c r="E5">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D6">
+        <v>30.4</v>
+      </c>
+      <c r="E6">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10">
+        <v>4.3</v>
+      </c>
+      <c r="D10">
+        <v>3.6</v>
+      </c>
+      <c r="E10">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11">
+        <v>9.5</v>
+      </c>
+      <c r="D11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12">
+        <v>0.7</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13">
+        <v>7.7</v>
+      </c>
+      <c r="D13">
+        <v>5.5</v>
+      </c>
+      <c r="E13">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14">
+        <v>5.9</v>
+      </c>
+      <c r="D14">
+        <v>1.5</v>
+      </c>
+      <c r="E14">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15">
+        <v>3.2</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
   <dimension ref="B3:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1435,7 +1590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
   <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1557,7 +1712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1693,7 +1848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
   <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1842,7 +1997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1927,7 +2082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2223,7 +2378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2465,7 +2620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C4:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2596,44 +2751,6 @@
       </c>
       <c r="H10" s="3">
         <v>-0.26600000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
-  <dimension ref="C14:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15">
-        <v>4.5419999999999998</v>
-      </c>
-      <c r="E15">
-        <v>4.8109999999999999</v>
-      </c>
-      <c r="F15">
-        <v>4.8289999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -2980,6 +3097,44 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
+  <dimension ref="C14:F15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>4.5419999999999998</v>
+      </c>
+      <c r="E15">
+        <v>4.8109999999999999</v>
+      </c>
+      <c r="F15">
+        <v>4.8289999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C14D998-9646-4685-BCE0-71E2922D8C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE617F0-C763-40A6-A848-A208A9C7FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="11" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -24,16 +24,17 @@
     <sheet name="Carteira" sheetId="16" r:id="rId9"/>
     <sheet name="Veículos" sheetId="21" r:id="rId10"/>
     <sheet name="Captações" sheetId="22" r:id="rId11"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId12"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId13"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId14"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId15"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId16"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId17"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId18"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId19"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId20"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId21"/>
+    <sheet name="Basiléia" sheetId="23" r:id="rId12"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId13"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId14"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId15"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId16"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId17"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId18"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId19"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId20"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId21"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="164">
   <si>
     <t>Labels</t>
   </si>
@@ -557,7 +558,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
@@ -616,11 +618,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -645,10 +648,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1455,6 +1460,75 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3955542-FD2E-4118-938C-50CACA7D889D}">
+  <dimension ref="C3:G21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C18" s="3">
+        <v>0.128</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C19" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C20" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C21" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.16699999999999998</v>
+      </c>
+      <c r="F21" s="18">
+        <v>-0.3</v>
+      </c>
+      <c r="G21" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
   <dimension ref="B3:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1590,7 +1664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
   <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1712,7 +1786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1848,7 +1922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
   <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1997,7 +2071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2082,7 +2156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2378,7 +2452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2613,144 +2687,6 @@
       </c>
       <c r="P11" s="16">
         <v>45992</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
-  <dimension ref="C4:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="F5">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.223</v>
-      </c>
-      <c r="H5" s="3">
-        <v>-0.33400000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>4.2649999999999997</v>
-      </c>
-      <c r="E6">
-        <v>3.9140000000000001</v>
-      </c>
-      <c r="F6">
-        <v>3.7949999999999999</v>
-      </c>
-      <c r="G6" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="H6" s="3">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E7">
-        <v>0.45700000000000002</v>
-      </c>
-      <c r="F7">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="G7" s="3">
-        <v>-0.13600000000000001</v>
-      </c>
-      <c r="H7" s="3">
-        <v>-0.248</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>3.83</v>
-      </c>
-      <c r="E8">
-        <v>4.5119999999999996</v>
-      </c>
-      <c r="F8">
-        <v>4.7969999999999997</v>
-      </c>
-      <c r="G8" s="3">
-        <v>6.3E-2</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.253</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>8.76</v>
-      </c>
-      <c r="E9">
-        <v>9.0030000000000001</v>
-      </c>
-      <c r="F9">
-        <v>9.08</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="G10" s="3">
-        <v>-0.154</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-0.26600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3097,6 +3033,144 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
+  <dimension ref="C4:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F5">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.223</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-0.33400000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>4.2649999999999997</v>
+      </c>
+      <c r="E6">
+        <v>3.9140000000000001</v>
+      </c>
+      <c r="F6">
+        <v>3.7949999999999999</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-0.03</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E7">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="F7">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-0.13600000000000001</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-0.248</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>3.83</v>
+      </c>
+      <c r="E8">
+        <v>4.5119999999999996</v>
+      </c>
+      <c r="F8">
+        <v>4.7969999999999997</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6.3E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>8.76</v>
+      </c>
+      <c r="E9">
+        <v>9.0030000000000001</v>
+      </c>
+      <c r="F9">
+        <v>9.08</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="3">
+        <v>-0.154</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-0.26600000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
   <dimension ref="C14:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3134,7 +3208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE617F0-C763-40A6-A848-A208A9C7FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A618C7AB-B5B8-4CFD-9D3F-67230B82BAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="11" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -23,18 +23,19 @@
     <sheet name="slide_11" sheetId="9" r:id="rId8"/>
     <sheet name="Carteira" sheetId="16" r:id="rId9"/>
     <sheet name="Veículos" sheetId="21" r:id="rId10"/>
-    <sheet name="Captações" sheetId="22" r:id="rId11"/>
-    <sheet name="Basiléia" sheetId="23" r:id="rId12"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId13"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId14"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId15"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId16"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId17"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId18"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId19"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId20"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId21"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId22"/>
+    <sheet name="Seguros e Cartões" sheetId="24" r:id="rId11"/>
+    <sheet name="Captações" sheetId="22" r:id="rId12"/>
+    <sheet name="Basiléia" sheetId="23" r:id="rId13"/>
+    <sheet name="slide_12" sheetId="10" r:id="rId14"/>
+    <sheet name="slide_13" sheetId="11" r:id="rId15"/>
+    <sheet name="slide_14" sheetId="12" r:id="rId16"/>
+    <sheet name="slide_15" sheetId="13" r:id="rId17"/>
+    <sheet name="slide_18" sheetId="14" r:id="rId18"/>
+    <sheet name="slide_20" sheetId="15" r:id="rId19"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId20"/>
+    <sheet name="Emprestimos" sheetId="4" r:id="rId21"/>
+    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId22"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="166">
   <si>
     <t>Labels</t>
   </si>
@@ -552,6 +553,12 @@
   </si>
   <si>
     <t>instrumentos de capital</t>
+  </si>
+  <si>
+    <t>Carteira de Veiculos</t>
+  </si>
+  <si>
+    <t>Pesados</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231522F5-4F73-43C4-84CE-1220F786E75E}">
-  <dimension ref="C3:K11"/>
+  <dimension ref="C3:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -1318,12 +1325,127 @@
         <v>4.12</v>
       </c>
     </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>52</v>
+      </c>
+      <c r="F20">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21">
+        <v>42.235999999999997</v>
+      </c>
+      <c r="E21">
+        <v>44.851999999999997</v>
+      </c>
+      <c r="F21">
+        <v>46.887999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22">
+        <v>2.2189999999999999</v>
+      </c>
+      <c r="E22">
+        <v>2.9129999999999998</v>
+      </c>
+      <c r="F22">
+        <v>3.258</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23">
+        <v>3.548</v>
+      </c>
+      <c r="E23">
+        <v>4.2619999999999996</v>
+      </c>
+      <c r="F23">
+        <v>4.5579999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71DEED7-F350-4CDE-A045-FE6552F7C104}">
+  <dimension ref="C3:I8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3">
+        <v>2024</v>
+      </c>
+      <c r="H3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>420</v>
+      </c>
+      <c r="E8">
+        <v>354</v>
+      </c>
+      <c r="F8">
+        <v>418</v>
+      </c>
+      <c r="G8">
+        <v>1672</v>
+      </c>
+      <c r="H8">
+        <v>1452</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088EF8FE-482E-42AC-8EA5-92878DC598D2}">
   <dimension ref="B3:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1459,7 +1581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3955542-FD2E-4118-938C-50CACA7D889D}">
   <dimension ref="C3:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1528,7 +1650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
   <dimension ref="B3:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1664,7 +1786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
   <dimension ref="B4:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1786,7 +1908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1922,7 +2044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
   <dimension ref="D2:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2071,7 +2193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
   <dimension ref="A3:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2156,7 +2278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2448,248 +2570,6 @@
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
-  <dimension ref="B7:P11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>5.6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>4.2</v>
-      </c>
-      <c r="G7">
-        <v>4.5</v>
-      </c>
-      <c r="H7">
-        <v>3.5</v>
-      </c>
-      <c r="I7">
-        <v>3.7</v>
-      </c>
-      <c r="J7">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K7">
-        <v>5.3</v>
-      </c>
-      <c r="L7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N7">
-        <v>4.3</v>
-      </c>
-      <c r="O7">
-        <v>4.8</v>
-      </c>
-      <c r="P7">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>5.5</v>
-      </c>
-      <c r="E8">
-        <v>4.7</v>
-      </c>
-      <c r="F8">
-        <v>4.8</v>
-      </c>
-      <c r="G8">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H8">
-        <v>4.3</v>
-      </c>
-      <c r="I8">
-        <v>4.7</v>
-      </c>
-      <c r="J8">
-        <v>6.2</v>
-      </c>
-      <c r="K8">
-        <v>6.4</v>
-      </c>
-      <c r="L8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M8">
-        <v>5.2</v>
-      </c>
-      <c r="N8">
-        <v>5.5</v>
-      </c>
-      <c r="O8">
-        <v>6.1</v>
-      </c>
-      <c r="P8">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E9">
-        <v>4.2</v>
-      </c>
-      <c r="F9">
-        <v>4.3</v>
-      </c>
-      <c r="G9">
-        <v>4.2</v>
-      </c>
-      <c r="H9">
-        <v>3.6</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
-      </c>
-      <c r="J9">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>5.6</v>
-      </c>
-      <c r="E10">
-        <v>1.8</v>
-      </c>
-      <c r="F10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G10">
-        <v>2.8</v>
-      </c>
-      <c r="H10">
-        <v>0.5</v>
-      </c>
-      <c r="I10">
-        <v>0.1</v>
-      </c>
-      <c r="J10">
-        <v>0.2</v>
-      </c>
-      <c r="K10">
-        <v>0.4</v>
-      </c>
-      <c r="L10">
-        <v>0.6</v>
-      </c>
-      <c r="M10">
-        <v>0.4</v>
-      </c>
-      <c r="N10">
-        <v>0.3</v>
-      </c>
-      <c r="O10">
-        <v>0.5</v>
-      </c>
-      <c r="P10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C11" s="16">
-        <v>42339</v>
-      </c>
-      <c r="D11" s="16">
-        <v>42705</v>
-      </c>
-      <c r="E11" s="16">
-        <v>43070</v>
-      </c>
-      <c r="F11" s="16">
-        <v>43435</v>
-      </c>
-      <c r="G11" s="16">
-        <v>43800</v>
-      </c>
-      <c r="H11" s="16">
-        <v>44166</v>
-      </c>
-      <c r="I11" s="16">
-        <v>44531</v>
-      </c>
-      <c r="J11" s="16">
-        <v>44896</v>
-      </c>
-      <c r="K11" s="16">
-        <v>45261</v>
-      </c>
-      <c r="L11" s="16">
-        <v>45627</v>
-      </c>
-      <c r="M11" s="16">
-        <v>45717</v>
-      </c>
-      <c r="N11" s="16">
-        <v>45809</v>
-      </c>
-      <c r="O11" s="16">
-        <v>45901</v>
-      </c>
-      <c r="P11" s="16">
-        <v>45992</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3033,6 +2913,248 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
+  <dimension ref="B7:P11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>5.6</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>4.2</v>
+      </c>
+      <c r="G7">
+        <v>4.5</v>
+      </c>
+      <c r="H7">
+        <v>3.5</v>
+      </c>
+      <c r="I7">
+        <v>3.7</v>
+      </c>
+      <c r="J7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K7">
+        <v>5.3</v>
+      </c>
+      <c r="L7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N7">
+        <v>4.3</v>
+      </c>
+      <c r="O7">
+        <v>4.8</v>
+      </c>
+      <c r="P7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>5.5</v>
+      </c>
+      <c r="E8">
+        <v>4.7</v>
+      </c>
+      <c r="F8">
+        <v>4.8</v>
+      </c>
+      <c r="G8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H8">
+        <v>4.3</v>
+      </c>
+      <c r="I8">
+        <v>4.7</v>
+      </c>
+      <c r="J8">
+        <v>6.2</v>
+      </c>
+      <c r="K8">
+        <v>6.4</v>
+      </c>
+      <c r="L8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M8">
+        <v>5.2</v>
+      </c>
+      <c r="N8">
+        <v>5.5</v>
+      </c>
+      <c r="O8">
+        <v>6.1</v>
+      </c>
+      <c r="P8">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E9">
+        <v>4.2</v>
+      </c>
+      <c r="F9">
+        <v>4.3</v>
+      </c>
+      <c r="G9">
+        <v>4.2</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>5.6</v>
+      </c>
+      <c r="E10">
+        <v>1.8</v>
+      </c>
+      <c r="F10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G10">
+        <v>2.8</v>
+      </c>
+      <c r="H10">
+        <v>0.5</v>
+      </c>
+      <c r="I10">
+        <v>0.1</v>
+      </c>
+      <c r="J10">
+        <v>0.2</v>
+      </c>
+      <c r="K10">
+        <v>0.4</v>
+      </c>
+      <c r="L10">
+        <v>0.6</v>
+      </c>
+      <c r="M10">
+        <v>0.4</v>
+      </c>
+      <c r="N10">
+        <v>0.3</v>
+      </c>
+      <c r="O10">
+        <v>0.5</v>
+      </c>
+      <c r="P10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C11" s="16">
+        <v>42339</v>
+      </c>
+      <c r="D11" s="16">
+        <v>42705</v>
+      </c>
+      <c r="E11" s="16">
+        <v>43070</v>
+      </c>
+      <c r="F11" s="16">
+        <v>43435</v>
+      </c>
+      <c r="G11" s="16">
+        <v>43800</v>
+      </c>
+      <c r="H11" s="16">
+        <v>44166</v>
+      </c>
+      <c r="I11" s="16">
+        <v>44531</v>
+      </c>
+      <c r="J11" s="16">
+        <v>44896</v>
+      </c>
+      <c r="K11" s="16">
+        <v>45261</v>
+      </c>
+      <c r="L11" s="16">
+        <v>45627</v>
+      </c>
+      <c r="M11" s="16">
+        <v>45717</v>
+      </c>
+      <c r="N11" s="16">
+        <v>45809</v>
+      </c>
+      <c r="O11" s="16">
+        <v>45901</v>
+      </c>
+      <c r="P11" s="16">
+        <v>45992</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C4:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3170,7 +3292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
   <dimension ref="C14:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3208,7 +3330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A618C7AB-B5B8-4CFD-9D3F-67230B82BAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D71E57F-B5F8-49BD-A8BA-B7F4CCB6E954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -18,24 +18,14 @@
     <sheet name="Qualidade Cart 4966" sheetId="20" r:id="rId3"/>
     <sheet name="DRE Saida" sheetId="1" r:id="rId4"/>
     <sheet name="Pizza Teste" sheetId="6" r:id="rId5"/>
-    <sheet name="slide_8" sheetId="7" r:id="rId6"/>
-    <sheet name="slide_9" sheetId="8" r:id="rId7"/>
-    <sheet name="slide_11" sheetId="9" r:id="rId8"/>
-    <sheet name="Carteira" sheetId="16" r:id="rId9"/>
-    <sheet name="Veículos" sheetId="21" r:id="rId10"/>
-    <sheet name="Seguros e Cartões" sheetId="24" r:id="rId11"/>
-    <sheet name="Captações" sheetId="22" r:id="rId12"/>
-    <sheet name="Basiléia" sheetId="23" r:id="rId13"/>
-    <sheet name="slide_12" sheetId="10" r:id="rId14"/>
-    <sheet name="slide_13" sheetId="11" r:id="rId15"/>
-    <sheet name="slide_14" sheetId="12" r:id="rId16"/>
-    <sheet name="slide_15" sheetId="13" r:id="rId17"/>
-    <sheet name="slide_18" sheetId="14" r:id="rId18"/>
-    <sheet name="slide_20" sheetId="15" r:id="rId19"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId20"/>
-    <sheet name="Emprestimos" sheetId="4" r:id="rId21"/>
-    <sheet name="Seguros e Cartoes" sheetId="5" r:id="rId22"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId23"/>
+    <sheet name="Carteira" sheetId="16" r:id="rId6"/>
+    <sheet name="Veículos" sheetId="21" r:id="rId7"/>
+    <sheet name="Seguros e Cartões" sheetId="24" r:id="rId8"/>
+    <sheet name="Captações" sheetId="22" r:id="rId9"/>
+    <sheet name="Basiléia" sheetId="23" r:id="rId10"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId11"/>
+    <sheet name="Empréstimos" sheetId="4" r:id="rId12"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="103">
   <si>
     <t>Labels</t>
   </si>
@@ -216,214 +206,25 @@
     <t>Receitas Totais</t>
   </si>
   <si>
-    <t>bilhoes</t>
-  </si>
-  <si>
-    <t>Graficos de Receitas totais</t>
-  </si>
-  <si>
     <t>Margem Financeira Bruta</t>
   </si>
   <si>
-    <t>Serviços e Seguros</t>
-  </si>
-  <si>
-    <t>Margem Financeira Bruta Total</t>
-  </si>
-  <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>clientes</t>
-  </si>
-  <si>
-    <t>Receitas De Serviços e Correetagem</t>
-  </si>
-  <si>
-    <t>Seguros</t>
-  </si>
-  <si>
-    <t>Servicos e Tarifas</t>
-  </si>
-  <si>
     <t>Custo de Crédito / Carteira de Crédito</t>
   </si>
   <si>
-    <t>PDD Expandida</t>
-  </si>
-  <si>
-    <t>Rec. De crédito</t>
-  </si>
-  <si>
-    <t>Custo de Crédito Sobre Carteira</t>
-  </si>
-  <si>
-    <t>Indice de Cobertura</t>
-  </si>
-  <si>
-    <t>Despesa Pessoal Administrativa</t>
-  </si>
-  <si>
-    <t>Pessoal</t>
-  </si>
-  <si>
-    <t>Administrativas</t>
-  </si>
-  <si>
-    <t>Deprec. Amortiza.</t>
-  </si>
-  <si>
-    <t>Indice de Eficiencia</t>
-  </si>
-  <si>
-    <t>Emprestimos</t>
-  </si>
-  <si>
     <t>Paineis Solares</t>
   </si>
   <si>
-    <t>Demais Veiculos</t>
-  </si>
-  <si>
-    <t>PMEs</t>
-  </si>
-  <si>
-    <t>Large Corporate</t>
-  </si>
-  <si>
-    <t>Originacao de Financiamentos de Veiculos</t>
-  </si>
-  <si>
-    <t>Médias</t>
-  </si>
-  <si>
     <t>Leves Usados</t>
   </si>
   <si>
-    <t>Depositos Interfinanceiros</t>
-  </si>
-  <si>
-    <t>Empréstimos e Repasses</t>
-  </si>
-  <si>
-    <t>Depositos a Prazo</t>
-  </si>
-  <si>
-    <t>Instrumentos de Capital</t>
-  </si>
-  <si>
-    <t>Cessões de Crédito</t>
-  </si>
-  <si>
     <t>FIDC</t>
   </si>
   <si>
-    <t>Titulos Emitidos no Exterior</t>
-  </si>
-  <si>
     <t>Letras Financeiras</t>
   </si>
   <si>
-    <t>Nivel II</t>
-  </si>
-  <si>
-    <t>Nivel I Complementar</t>
-  </si>
-  <si>
-    <t>Nivel I Principal</t>
-  </si>
-  <si>
-    <t>Indice Basileia</t>
-  </si>
-  <si>
-    <t>3T25 vs 2t</t>
-  </si>
-  <si>
-    <t>Capital 2T25</t>
-  </si>
-  <si>
-    <t>Lucro Liquido JCP</t>
-  </si>
-  <si>
-    <t>Nivel 1 Compl.</t>
-  </si>
-  <si>
-    <t>Ajustes Prud</t>
-  </si>
-  <si>
-    <t>Capital</t>
-  </si>
-  <si>
     <t>Outros Veiculos</t>
-  </si>
-  <si>
-    <t>Premios de Seguros</t>
-  </si>
-  <si>
-    <t>CIB</t>
-  </si>
-  <si>
-    <t>CORPORATE</t>
-  </si>
-  <si>
-    <t>LARGE + if</t>
-  </si>
-  <si>
-    <t>Exposicao de Carteira Do atacado</t>
-  </si>
-  <si>
-    <t>Agroindustria</t>
-  </si>
-  <si>
-    <t>Inst. Financeiras</t>
-  </si>
-  <si>
-    <t>Industria</t>
-  </si>
-  <si>
-    <t>Servicos</t>
-  </si>
-  <si>
-    <t>Acucar e Etanol</t>
-  </si>
-  <si>
-    <t>Construcao Civil</t>
-  </si>
-  <si>
-    <t>Telecomunicacoes</t>
-  </si>
-  <si>
-    <t>Cooperativas</t>
-  </si>
-  <si>
-    <t>Oleo e Gas</t>
-  </si>
-  <si>
-    <t>Project Finance</t>
-  </si>
-  <si>
-    <t>Montadoras</t>
-  </si>
-  <si>
-    <t>Mineracao</t>
-  </si>
-  <si>
-    <t>Energia Eletrica</t>
-  </si>
-  <si>
-    <t>Locadoras</t>
-  </si>
-  <si>
-    <t>Saude</t>
-  </si>
-  <si>
-    <t>Saneamento</t>
-  </si>
-  <si>
-    <t>Farmaceutico</t>
-  </si>
-  <si>
-    <t>Outros</t>
   </si>
   <si>
     <t>4T25</t>
@@ -565,10 +366,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -630,7 +430,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -641,20 +441,11 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1006,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>2024</v>
@@ -1037,7 +828,7 @@
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>2519</v>
@@ -1057,7 +848,7 @@
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="D6">
         <v>2367</v>
@@ -1077,7 +868,7 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="D7">
         <v>152</v>
@@ -1097,7 +888,7 @@
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="D9">
         <v>695</v>
@@ -1160,428 +951,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231522F5-4F73-43C4-84CE-1220F786E75E}">
-  <dimension ref="C3:K23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3">
-        <v>2024</v>
-      </c>
-      <c r="H3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.27</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.29099999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6">
-        <v>49</v>
-      </c>
-      <c r="E6">
-        <v>49</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>49</v>
-      </c>
-      <c r="H6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="E7">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="F7">
-        <v>39.5</v>
-      </c>
-      <c r="G7">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="H7">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8">
-        <v>85.8</v>
-      </c>
-      <c r="E8">
-        <v>83.1</v>
-      </c>
-      <c r="F8">
-        <v>84.2</v>
-      </c>
-      <c r="G8">
-        <v>85.8</v>
-      </c>
-      <c r="H8">
-        <v>84.2</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D9">
-        <v>7.1</v>
-      </c>
-      <c r="E9">
-        <v>6.5</v>
-      </c>
-      <c r="F9">
-        <v>8.1</v>
-      </c>
-      <c r="G9">
-        <v>28.3</v>
-      </c>
-      <c r="H9">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10">
-        <v>6.1260000000000003</v>
-      </c>
-      <c r="E10">
-        <v>5.4009999999999998</v>
-      </c>
-      <c r="F10">
-        <v>6.7850000000000001</v>
-      </c>
-      <c r="G10">
-        <v>24.265999999999998</v>
-      </c>
-      <c r="H10">
-        <v>21.97</v>
-      </c>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11">
-        <v>1.0109999999999999</v>
-      </c>
-      <c r="E11">
-        <v>1.101</v>
-      </c>
-      <c r="F11">
-        <v>1.272</v>
-      </c>
-      <c r="G11">
-        <v>4.0049999999999999</v>
-      </c>
-      <c r="H11">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20">
-        <v>48</v>
-      </c>
-      <c r="E20">
-        <v>52</v>
-      </c>
-      <c r="F20">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21">
-        <v>42.235999999999997</v>
-      </c>
-      <c r="E21">
-        <v>44.851999999999997</v>
-      </c>
-      <c r="F21">
-        <v>46.887999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22">
-        <v>2.2189999999999999</v>
-      </c>
-      <c r="E22">
-        <v>2.9129999999999998</v>
-      </c>
-      <c r="F22">
-        <v>3.258</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23">
-        <v>3.548</v>
-      </c>
-      <c r="E23">
-        <v>4.2619999999999996</v>
-      </c>
-      <c r="F23">
-        <v>4.5579999999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71DEED7-F350-4CDE-A045-FE6552F7C104}">
-  <dimension ref="C3:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3">
-        <v>2024</v>
-      </c>
-      <c r="H3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>420</v>
-      </c>
-      <c r="E8">
-        <v>354</v>
-      </c>
-      <c r="F8">
-        <v>418</v>
-      </c>
-      <c r="G8">
-        <v>1672</v>
-      </c>
-      <c r="H8">
-        <v>1452</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088EF8FE-482E-42AC-8EA5-92878DC598D2}">
-  <dimension ref="B3:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5">
-        <v>35.5</v>
-      </c>
-      <c r="D5">
-        <v>41.9</v>
-      </c>
-      <c r="E5">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="D6">
-        <v>30.4</v>
-      </c>
-      <c r="E6">
-        <v>34.799999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10">
-        <v>4.3</v>
-      </c>
-      <c r="D10">
-        <v>3.6</v>
-      </c>
-      <c r="E10">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11">
-        <v>9.5</v>
-      </c>
-      <c r="D11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E11">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12">
-        <v>0.7</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13">
-        <v>7.7</v>
-      </c>
-      <c r="D13">
-        <v>5.5</v>
-      </c>
-      <c r="E13">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C14">
-        <v>5.9</v>
-      </c>
-      <c r="D14">
-        <v>1.5</v>
-      </c>
-      <c r="E14">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15">
-        <v>3.2</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3955542-FD2E-4118-938C-50CACA7D889D}">
   <dimension ref="C3:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1594,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="3:7" x14ac:dyDescent="0.25">
@@ -1640,7 +1009,7 @@
       <c r="E21" s="3">
         <v>0.16699999999999998</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="13">
         <v>-0.3</v>
       </c>
       <c r="G21" s="3"/>
@@ -1650,135 +1019,241 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4745116-4A8C-412D-BBE6-45B5E5EC0DB3}">
-  <dimension ref="B3:E11"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
+  <dimension ref="B7:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>5.6</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>4.2</v>
+      </c>
+      <c r="G7">
+        <v>4.5</v>
+      </c>
+      <c r="H7">
+        <v>3.5</v>
+      </c>
+      <c r="I7">
+        <v>3.7</v>
+      </c>
+      <c r="J7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K7">
+        <v>5.3</v>
+      </c>
+      <c r="L7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N7">
+        <v>4.3</v>
+      </c>
+      <c r="O7">
+        <v>4.8</v>
+      </c>
+      <c r="P7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>5.5</v>
+      </c>
+      <c r="E8">
+        <v>4.7</v>
+      </c>
+      <c r="F8">
+        <v>4.8</v>
+      </c>
+      <c r="G8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H8">
+        <v>4.3</v>
+      </c>
+      <c r="I8">
+        <v>4.7</v>
+      </c>
+      <c r="J8">
+        <v>6.2</v>
+      </c>
+      <c r="K8">
+        <v>6.4</v>
+      </c>
+      <c r="L8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M8">
+        <v>5.2</v>
+      </c>
+      <c r="N8">
+        <v>5.5</v>
+      </c>
+      <c r="O8">
+        <v>6.1</v>
+      </c>
+      <c r="P8">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4">
-        <v>0.7</v>
-      </c>
-      <c r="D4">
+      <c r="D9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E9">
+        <v>4.2</v>
+      </c>
+      <c r="F9">
+        <v>4.3</v>
+      </c>
+      <c r="G9">
+        <v>4.2</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>5.6</v>
+      </c>
+      <c r="E10">
+        <v>1.8</v>
+      </c>
+      <c r="F10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G10">
+        <v>2.8</v>
+      </c>
+      <c r="H10">
+        <v>0.5</v>
+      </c>
+      <c r="I10">
+        <v>0.1</v>
+      </c>
+      <c r="J10">
+        <v>0.2</v>
+      </c>
+      <c r="K10">
+        <v>0.4</v>
+      </c>
+      <c r="L10">
         <v>0.6</v>
       </c>
-      <c r="E4">
+      <c r="M10">
+        <v>0.4</v>
+      </c>
+      <c r="N10">
+        <v>0.3</v>
+      </c>
+      <c r="O10">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-      <c r="D5">
-        <v>4.8</v>
-      </c>
-      <c r="E5">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>3.8</v>
-      </c>
-      <c r="D6">
-        <v>4.5</v>
-      </c>
-      <c r="E6">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7">
-        <v>4.3</v>
-      </c>
-      <c r="D7">
-        <v>3.9</v>
-      </c>
-      <c r="E7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-      <c r="D8">
-        <v>6.7</v>
-      </c>
-      <c r="E8">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9">
-        <v>45.6</v>
-      </c>
-      <c r="D9">
-        <v>44.7</v>
-      </c>
-      <c r="E9">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D10">
-        <v>2.5</v>
-      </c>
-      <c r="E10">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11">
-        <v>23.7</v>
-      </c>
-      <c r="D11">
-        <v>23.5</v>
-      </c>
-      <c r="E11">
-        <v>23.9</v>
+      <c r="P10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C11" s="12">
+        <v>42339</v>
+      </c>
+      <c r="D11" s="12">
+        <v>42705</v>
+      </c>
+      <c r="E11" s="12">
+        <v>43070</v>
+      </c>
+      <c r="F11" s="12">
+        <v>43435</v>
+      </c>
+      <c r="G11" s="12">
+        <v>43800</v>
+      </c>
+      <c r="H11" s="12">
+        <v>44166</v>
+      </c>
+      <c r="I11" s="12">
+        <v>44531</v>
+      </c>
+      <c r="J11" s="12">
+        <v>44896</v>
+      </c>
+      <c r="K11" s="12">
+        <v>45261</v>
+      </c>
+      <c r="L11" s="12">
+        <v>45627</v>
+      </c>
+      <c r="M11" s="12">
+        <v>45717</v>
+      </c>
+      <c r="N11" s="12">
+        <v>45809</v>
+      </c>
+      <c r="O11" s="12">
+        <v>45901</v>
+      </c>
+      <c r="P11" s="12">
+        <v>45992</v>
       </c>
     </row>
   </sheetData>
@@ -1786,790 +1261,219 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC81BA9-A722-4D51-8849-833605DBA551}">
-  <dimension ref="B4:O7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="J4" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F6" s="10">
-        <v>3.1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>3</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0.42</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="12">
-        <v>6.4</v>
-      </c>
-      <c r="D7" s="12">
-        <v>4.7</v>
-      </c>
-      <c r="E7" s="12">
-        <v>5.4</v>
-      </c>
-      <c r="F7" s="12">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="G7" s="12">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="J4:O4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB40F4D6-7254-451B-8F15-55583AC6E46C}">
-  <dimension ref="B2:E10"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
+  <dimension ref="C3:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3">
-        <v>5.5</v>
-      </c>
-      <c r="D3">
-        <v>1.3</v>
-      </c>
-      <c r="E3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4">
-        <v>6.5</v>
-      </c>
-      <c r="D4">
-        <v>5.3</v>
-      </c>
-      <c r="E4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5">
-        <v>37.1</v>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>28.4</v>
+        <v>169</v>
       </c>
       <c r="E5">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6">
-        <v>3.2</v>
+        <v>93</v>
+      </c>
+      <c r="F5">
+        <v>74</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-0.20499999999999999</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-0.56299999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>3.4</v>
+        <v>4167</v>
       </c>
       <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7">
-        <v>10.4</v>
+        <v>3795</v>
+      </c>
+      <c r="F6">
+        <v>3731</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>6.8</v>
+        <v>513</v>
       </c>
       <c r="E7">
-        <v>8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <v>0.7</v>
+        <v>395</v>
+      </c>
+      <c r="F7">
+        <v>333</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.157</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-0.35099999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0.8</v>
+        <v>4032</v>
       </c>
       <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9">
-        <v>4.2</v>
+        <v>4797</v>
+      </c>
+      <c r="F8">
+        <v>5262</v>
+      </c>
+      <c r="G8" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.30499999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>7.2</v>
+        <v>8881</v>
       </c>
       <c r="E9">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10">
-        <v>35</v>
-      </c>
-      <c r="D10">
-        <v>40.799999999999997</v>
-      </c>
-      <c r="E10">
-        <v>41.9</v>
-      </c>
+        <v>9080</v>
+      </c>
+      <c r="F9">
+        <v>9400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DDA400-E7C3-412D-BF6F-6237B27DC1D6}">
-  <dimension ref="D2:O7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-    </row>
-    <row r="3" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1.4E-2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>2.4E-2</v>
-      </c>
-      <c r="J5" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3">
-        <v>2.4E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.13</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.127</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.129</v>
-      </c>
-      <c r="J6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.127</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3">
-        <v>0.129</v>
-      </c>
-    </row>
-    <row r="7" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216C394-E57F-4E0F-A385-35E21DA9536A}">
-  <dimension ref="A3:N5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4">
-        <v>5.5</v>
-      </c>
-      <c r="C4">
-        <v>6.7</v>
-      </c>
-      <c r="D4">
-        <v>7.2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4">
-        <v>441.7</v>
-      </c>
-      <c r="K4">
-        <v>314.2</v>
-      </c>
-      <c r="L4">
-        <v>354.2</v>
-      </c>
-      <c r="M4">
-        <v>1252.4000000000001</v>
-      </c>
-      <c r="N4">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5">
-        <v>45.6</v>
-      </c>
-      <c r="C5">
-        <v>44.7</v>
-      </c>
-      <c r="D5">
-        <v>44.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C78759-C237-4426-A1F9-93877BD87587}">
-  <dimension ref="A1:I22"/>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
+  <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="G1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="3" spans="23:37" x14ac:dyDescent="0.25">
+      <c r="W3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="AB3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="AE3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C3">
-        <v>2.5</v>
-      </c>
-      <c r="D3">
-        <v>2.8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3">
+      <c r="AJ3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK3" t="s">
         <v>12</v>
       </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4">
-        <v>13.2</v>
-      </c>
-      <c r="C4">
-        <v>13.6</v>
-      </c>
-      <c r="D4">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4">
-        <v>12</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5">
-        <v>10.5</v>
-      </c>
-      <c r="C5">
+    </row>
+    <row r="9" spans="23:37" x14ac:dyDescent="0.25">
+      <c r="W9">
         <v>9.9</v>
       </c>
-      <c r="D5">
+      <c r="X9">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G10" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
-      <c r="I12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H14">
-        <v>3</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G15" t="s">
-        <v>113</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G17" t="s">
-        <v>115</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G19" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G20" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G21" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G22" t="s">
-        <v>120</v>
-      </c>
-      <c r="H22">
-        <v>13</v>
-      </c>
-      <c r="I22">
-        <v>18</v>
+      <c r="Y9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Z9">
+        <v>9.6</v>
+      </c>
+      <c r="AA9">
+        <v>9.9</v>
+      </c>
+      <c r="AB9">
+        <v>11.1</v>
+      </c>
+      <c r="AC9">
+        <v>9.9</v>
+      </c>
+      <c r="AD9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AE9">
+        <v>9.5</v>
+      </c>
+      <c r="AJ9">
+        <v>9.6</v>
+      </c>
+      <c r="AK9">
+        <v>9.6999999999999993</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2584,7 +1488,7 @@
   <sheetData>
     <row r="2" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -2593,7 +1497,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>2024</v>
@@ -2604,7 +1508,7 @@
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>187</v>
@@ -2633,7 +1537,7 @@
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>776</v>
@@ -2662,7 +1566,7 @@
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3">
         <v>3.4000000000000002E-2</v>
@@ -2681,7 +1585,7 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="15"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D13">
@@ -2717,7 +1621,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="G16">
         <v>2024</v>
@@ -2727,11 +1631,11 @@
       </c>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="14"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="D19">
         <v>239</v>
@@ -2751,7 +1655,7 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="D26">
         <v>695</v>
@@ -2771,7 +1675,7 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="D28">
         <v>457</v>
@@ -2790,7 +1694,7 @@
       </c>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F31" s="14"/>
+      <c r="F31" s="10"/>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
@@ -2800,7 +1704,7 @@
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="G33">
         <v>2024</v>
@@ -2811,7 +1715,7 @@
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D35">
         <v>520</v>
@@ -2831,7 +1735,7 @@
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="D39">
         <v>398</v>
@@ -2851,7 +1755,7 @@
     </row>
     <row r="45" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="D45">
         <v>98</v>
@@ -2880,7 +1784,7 @@
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="D47">
         <v>1015</v>
@@ -2909,504 +1813,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
-  <dimension ref="B7:P11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>5.6</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>4.2</v>
-      </c>
-      <c r="G7">
-        <v>4.5</v>
-      </c>
-      <c r="H7">
-        <v>3.5</v>
-      </c>
-      <c r="I7">
-        <v>3.7</v>
-      </c>
-      <c r="J7">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K7">
-        <v>5.3</v>
-      </c>
-      <c r="L7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N7">
-        <v>4.3</v>
-      </c>
-      <c r="O7">
-        <v>4.8</v>
-      </c>
-      <c r="P7">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>5.5</v>
-      </c>
-      <c r="E8">
-        <v>4.7</v>
-      </c>
-      <c r="F8">
-        <v>4.8</v>
-      </c>
-      <c r="G8">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H8">
-        <v>4.3</v>
-      </c>
-      <c r="I8">
-        <v>4.7</v>
-      </c>
-      <c r="J8">
-        <v>6.2</v>
-      </c>
-      <c r="K8">
-        <v>6.4</v>
-      </c>
-      <c r="L8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M8">
-        <v>5.2</v>
-      </c>
-      <c r="N8">
-        <v>5.5</v>
-      </c>
-      <c r="O8">
-        <v>6.1</v>
-      </c>
-      <c r="P8">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E9">
-        <v>4.2</v>
-      </c>
-      <c r="F9">
-        <v>4.3</v>
-      </c>
-      <c r="G9">
-        <v>4.2</v>
-      </c>
-      <c r="H9">
-        <v>3.6</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
-      </c>
-      <c r="J9">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>5.6</v>
-      </c>
-      <c r="E10">
-        <v>1.8</v>
-      </c>
-      <c r="F10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G10">
-        <v>2.8</v>
-      </c>
-      <c r="H10">
-        <v>0.5</v>
-      </c>
-      <c r="I10">
-        <v>0.1</v>
-      </c>
-      <c r="J10">
-        <v>0.2</v>
-      </c>
-      <c r="K10">
-        <v>0.4</v>
-      </c>
-      <c r="L10">
-        <v>0.6</v>
-      </c>
-      <c r="M10">
-        <v>0.4</v>
-      </c>
-      <c r="N10">
-        <v>0.3</v>
-      </c>
-      <c r="O10">
-        <v>0.5</v>
-      </c>
-      <c r="P10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C11" s="16">
-        <v>42339</v>
-      </c>
-      <c r="D11" s="16">
-        <v>42705</v>
-      </c>
-      <c r="E11" s="16">
-        <v>43070</v>
-      </c>
-      <c r="F11" s="16">
-        <v>43435</v>
-      </c>
-      <c r="G11" s="16">
-        <v>43800</v>
-      </c>
-      <c r="H11" s="16">
-        <v>44166</v>
-      </c>
-      <c r="I11" s="16">
-        <v>44531</v>
-      </c>
-      <c r="J11" s="16">
-        <v>44896</v>
-      </c>
-      <c r="K11" s="16">
-        <v>45261</v>
-      </c>
-      <c r="L11" s="16">
-        <v>45627</v>
-      </c>
-      <c r="M11" s="16">
-        <v>45717</v>
-      </c>
-      <c r="N11" s="16">
-        <v>45809</v>
-      </c>
-      <c r="O11" s="16">
-        <v>45901</v>
-      </c>
-      <c r="P11" s="16">
-        <v>45992</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
-  <dimension ref="C4:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="F5">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.223</v>
-      </c>
-      <c r="H5" s="3">
-        <v>-0.33400000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>4.2649999999999997</v>
-      </c>
-      <c r="E6">
-        <v>3.9140000000000001</v>
-      </c>
-      <c r="F6">
-        <v>3.7949999999999999</v>
-      </c>
-      <c r="G6" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="H6" s="3">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E7">
-        <v>0.45700000000000002</v>
-      </c>
-      <c r="F7">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="G7" s="3">
-        <v>-0.13600000000000001</v>
-      </c>
-      <c r="H7" s="3">
-        <v>-0.248</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>3.83</v>
-      </c>
-      <c r="E8">
-        <v>4.5119999999999996</v>
-      </c>
-      <c r="F8">
-        <v>4.7969999999999997</v>
-      </c>
-      <c r="G8" s="3">
-        <v>6.3E-2</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.253</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>8.76</v>
-      </c>
-      <c r="E9">
-        <v>9.0030000000000001</v>
-      </c>
-      <c r="F9">
-        <v>9.08</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="G10" s="3">
-        <v>-0.154</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-0.26600000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A3B47-E08A-478E-9E32-E383F8DD5BE7}">
-  <dimension ref="C14:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15">
-        <v>4.5419999999999998</v>
-      </c>
-      <c r="E15">
-        <v>4.8109999999999999</v>
-      </c>
-      <c r="F15">
-        <v>4.8289999999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
-  <dimension ref="W3:AK9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="23:37" x14ac:dyDescent="0.25">
-      <c r="W3" t="s">
-        <v>1</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="23:37" x14ac:dyDescent="0.25">
-      <c r="W9">
-        <v>9.9</v>
-      </c>
-      <c r="X9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="Y9">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="Z9">
-        <v>9.6</v>
-      </c>
-      <c r="AA9">
-        <v>9.9</v>
-      </c>
-      <c r="AB9">
-        <v>11.1</v>
-      </c>
-      <c r="AC9">
-        <v>9.9</v>
-      </c>
-      <c r="AD9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AE9">
-        <v>9.5</v>
-      </c>
-      <c r="AJ9">
-        <v>9.6</v>
-      </c>
-      <c r="AK9">
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3423,17 +1829,17 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>1.68</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>1.78</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>1.69</v>
       </c>
     </row>
@@ -5473,540 +3879,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23508980-3939-4D95-9A4C-23A64D6BD062}">
-  <dimension ref="C3:J27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="25.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C4">
-        <v>2.9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>2372</v>
-      </c>
-      <c r="E10">
-        <v>685</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10">
-        <v>6782</v>
-      </c>
-      <c r="I10">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11">
-        <v>2311</v>
-      </c>
-      <c r="E11">
-        <v>556</v>
-      </c>
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11">
-        <v>6976</v>
-      </c>
-      <c r="I11">
-        <v>1798</v>
-      </c>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>2295</v>
-      </c>
-      <c r="E12">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="J13" s="1"/>
-    </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18">
-        <v>284</v>
-      </c>
-      <c r="E18">
-        <v>2088</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18">
-        <v>796</v>
-      </c>
-      <c r="I18">
-        <v>5986</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19">
-        <v>232</v>
-      </c>
-      <c r="E19">
-        <v>2079</v>
-      </c>
-      <c r="G19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19">
-        <v>793</v>
-      </c>
-      <c r="I19">
-        <v>6183</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20">
-        <v>244</v>
-      </c>
-      <c r="E20">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25">
-        <v>241</v>
-      </c>
-      <c r="E25">
-        <v>444</v>
-      </c>
-      <c r="G25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25">
-        <v>693</v>
-      </c>
-      <c r="I25">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26">
-        <v>165</v>
-      </c>
-      <c r="E26">
-        <v>391</v>
-      </c>
-      <c r="G26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26">
-        <v>585</v>
-      </c>
-      <c r="I26">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27">
-        <v>205</v>
-      </c>
-      <c r="E27">
-        <v>419</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FAFF65-4D1E-443F-BDF3-D7DA42FEA733}">
-  <dimension ref="B2:P7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="K2" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="3">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="G4" s="3">
-        <v>3.9E-2</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1.72</v>
-      </c>
-      <c r="L4" s="9">
-        <v>1.68</v>
-      </c>
-      <c r="M4" s="9">
-        <v>2.21</v>
-      </c>
-      <c r="N4" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="O4" s="9">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6">
-        <v>1159</v>
-      </c>
-      <c r="D6">
-        <v>1167</v>
-      </c>
-      <c r="E6">
-        <v>972</v>
-      </c>
-      <c r="F6">
-        <v>3275</v>
-      </c>
-      <c r="G6">
-        <v>3170</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7">
-        <v>-155</v>
-      </c>
-      <c r="D7">
-        <v>-243</v>
-      </c>
-      <c r="E7">
-        <v>-92</v>
-      </c>
-      <c r="F7">
-        <v>-458</v>
-      </c>
-      <c r="G7">
-        <v>-501</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="K2:P2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B33BFE8-86C2-496F-B733-78BC5607B7C2}">
-  <dimension ref="B2:O6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="J2" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="11">
-        <v>472</v>
-      </c>
-      <c r="D4" s="11">
-        <v>450</v>
-      </c>
-      <c r="E4" s="11">
-        <v>494</v>
-      </c>
-      <c r="F4" s="11">
-        <v>1317</v>
-      </c>
-      <c r="G4" s="11">
-        <v>1411</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0.377</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.379</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0.373</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.373</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5">
-        <v>349</v>
-      </c>
-      <c r="D5">
-        <v>346</v>
-      </c>
-      <c r="E5">
-        <v>311</v>
-      </c>
-      <c r="F5">
-        <v>981</v>
-      </c>
-      <c r="G5">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6">
-        <v>102</v>
-      </c>
-      <c r="D6">
-        <v>110</v>
-      </c>
-      <c r="E6">
-        <v>113</v>
-      </c>
-      <c r="F6">
-        <v>309</v>
-      </c>
-      <c r="G6">
-        <v>332</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3790767E-187D-4BED-BBAB-0D1EEC80F334}">
   <dimension ref="C12:N120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6026,34 +3898,34 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="13">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="9">
         <v>61464</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="9">
         <v>65935</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="9">
         <v>69333</v>
       </c>
     </row>
-    <row r="15" spans="3:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="13">
+    <row r="15" spans="3:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="9">
         <v>52789</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="9">
         <v>56267</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="9">
         <v>58802</v>
       </c>
     </row>
@@ -6073,7 +3945,7 @@
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="D17">
         <v>2219</v>
@@ -6087,7 +3959,7 @@
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="D18">
         <v>3548</v>
@@ -6101,7 +3973,7 @@
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D19">
         <v>4167</v>
@@ -6129,7 +4001,7 @@
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="D21">
         <v>106</v>
@@ -6141,23 +4013,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="3:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="13">
+    <row r="22" spans="3:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="9">
         <v>8857</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="9">
         <v>9668</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="9">
         <v>10531</v>
       </c>
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="D23">
         <v>4032</v>
@@ -6171,7 +4043,7 @@
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D24">
         <v>4765</v>
@@ -6185,7 +4057,7 @@
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="D25">
         <v>60</v>
@@ -6198,18 +4070,18 @@
       </c>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="3:14" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:14" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C27" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" s="13">
+      <c r="C27" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="9">
         <v>12884</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="9">
         <v>9628</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="9">
         <v>10318</v>
       </c>
     </row>
@@ -6229,7 +4101,7 @@
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="D29">
         <v>5114</v>
@@ -6243,7 +4115,7 @@
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="D30">
         <v>1343</v>
@@ -6256,22 +4128,22 @@
       </c>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C34" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="13">
+      <c r="C34" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="9">
         <v>28856</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="9">
         <v>26665</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="9">
         <v>28323</v>
       </c>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="D35">
         <v>6008</v>
@@ -6285,7 +4157,7 @@
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D36">
         <v>9964</v>
@@ -6299,7 +4171,7 @@
     </row>
     <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="D40">
         <v>90502</v>
@@ -6319,12 +4191,12 @@
         <v>9</v>
       </c>
       <c r="F115" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="D117">
         <v>14043</v>
@@ -6338,7 +4210,7 @@
     </row>
     <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="D118">
         <v>11864</v>
@@ -6366,7 +4238,7 @@
     </row>
     <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="D120">
         <v>28856</v>
@@ -6376,6 +4248,458 @@
       </c>
       <c r="F120">
         <v>28323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231522F5-4F73-43C4-84CE-1220F786E75E}">
+  <dimension ref="C3:K23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>2024</v>
+      </c>
+      <c r="H3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>49</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>49</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="E7">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F7">
+        <v>39.5</v>
+      </c>
+      <c r="G7">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="H7">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8">
+        <v>85.8</v>
+      </c>
+      <c r="E8">
+        <v>83.1</v>
+      </c>
+      <c r="F8">
+        <v>84.2</v>
+      </c>
+      <c r="G8">
+        <v>85.8</v>
+      </c>
+      <c r="H8">
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9">
+        <v>7.1</v>
+      </c>
+      <c r="E9">
+        <v>6.5</v>
+      </c>
+      <c r="F9">
+        <v>8.1</v>
+      </c>
+      <c r="G9">
+        <v>28.3</v>
+      </c>
+      <c r="H9">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10">
+        <v>6.1260000000000003</v>
+      </c>
+      <c r="E10">
+        <v>5.4009999999999998</v>
+      </c>
+      <c r="F10">
+        <v>6.7850000000000001</v>
+      </c>
+      <c r="G10">
+        <v>24.265999999999998</v>
+      </c>
+      <c r="H10">
+        <v>21.97</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="E11">
+        <v>1.101</v>
+      </c>
+      <c r="F11">
+        <v>1.272</v>
+      </c>
+      <c r="G11">
+        <v>4.0049999999999999</v>
+      </c>
+      <c r="H11">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>52</v>
+      </c>
+      <c r="F20">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21">
+        <v>42.235999999999997</v>
+      </c>
+      <c r="E21">
+        <v>44.851999999999997</v>
+      </c>
+      <c r="F21">
+        <v>46.887999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22">
+        <v>2.2189999999999999</v>
+      </c>
+      <c r="E22">
+        <v>2.9129999999999998</v>
+      </c>
+      <c r="F22">
+        <v>3.258</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23">
+        <v>3.548</v>
+      </c>
+      <c r="E23">
+        <v>4.2619999999999996</v>
+      </c>
+      <c r="F23">
+        <v>4.5579999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71DEED7-F350-4CDE-A045-FE6552F7C104}">
+  <dimension ref="C3:I15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>2024</v>
+      </c>
+      <c r="H3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>420</v>
+      </c>
+      <c r="E8">
+        <v>354</v>
+      </c>
+      <c r="F8">
+        <v>418</v>
+      </c>
+      <c r="G8">
+        <v>1672</v>
+      </c>
+      <c r="H8">
+        <v>1452</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>4761</v>
+      </c>
+      <c r="E15">
+        <v>4829</v>
+      </c>
+      <c r="F15">
+        <v>5230</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088EF8FE-482E-42AC-8EA5-92878DC598D2}">
+  <dimension ref="B3:E15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>35.5</v>
+      </c>
+      <c r="D5">
+        <v>41.9</v>
+      </c>
+      <c r="E5">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D6">
+        <v>30.4</v>
+      </c>
+      <c r="E6">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10">
+        <v>4.3</v>
+      </c>
+      <c r="D10">
+        <v>3.6</v>
+      </c>
+      <c r="E10">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11">
+        <v>9.5</v>
+      </c>
+      <c r="D11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <v>0.7</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13">
+        <v>7.7</v>
+      </c>
+      <c r="D13">
+        <v>5.5</v>
+      </c>
+      <c r="E13">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14">
+        <v>5.9</v>
+      </c>
+      <c r="D14">
+        <v>1.5</v>
+      </c>
+      <c r="E14">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>3.2</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>4.0999999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D71E57F-B5F8-49BD-A8BA-B7F4CCB6E954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B88A98-8B26-43E9-83A4-B36059BA0ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="6" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="DRE Saida" sheetId="1" r:id="rId4"/>
     <sheet name="Pizza Teste" sheetId="6" r:id="rId5"/>
     <sheet name="Carteira" sheetId="16" r:id="rId6"/>
-    <sheet name="Veículos" sheetId="21" r:id="rId7"/>
-    <sheet name="Seguros e Cartões" sheetId="24" r:id="rId8"/>
-    <sheet name="Captações" sheetId="22" r:id="rId9"/>
-    <sheet name="Basiléia" sheetId="23" r:id="rId10"/>
-    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId11"/>
-    <sheet name="Empréstimos" sheetId="4" r:id="rId12"/>
-    <sheet name="Margem Financeira" sheetId="2" r:id="rId13"/>
+    <sheet name="Carteira Atac Setor" sheetId="25" r:id="rId7"/>
+    <sheet name="Veículos" sheetId="21" r:id="rId8"/>
+    <sheet name="Seguros e Cartões" sheetId="24" r:id="rId9"/>
+    <sheet name="Captações" sheetId="22" r:id="rId10"/>
+    <sheet name="Basiléia" sheetId="23" r:id="rId11"/>
+    <sheet name="Qualidade Cart 2682" sheetId="3" r:id="rId12"/>
+    <sheet name="Empréstimos" sheetId="4" r:id="rId13"/>
+    <sheet name="Margem Financeira" sheetId="2" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="125">
   <si>
     <t>Labels</t>
   </si>
@@ -360,6 +361,72 @@
   </si>
   <si>
     <t>Pesados</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Setor</t>
+  </si>
+  <si>
+    <t>Setor 1</t>
+  </si>
+  <si>
+    <t>Setor 2</t>
+  </si>
+  <si>
+    <t>Setor 3</t>
+  </si>
+  <si>
+    <t>Setor 4</t>
+  </si>
+  <si>
+    <t>Setor 5</t>
+  </si>
+  <si>
+    <t>Setor 6</t>
+  </si>
+  <si>
+    <t>Setor 7</t>
+  </si>
+  <si>
+    <t>Setor 8</t>
+  </si>
+  <si>
+    <t>Setor 9</t>
+  </si>
+  <si>
+    <t>Setor 10</t>
+  </si>
+  <si>
+    <t>Setor 11</t>
+  </si>
+  <si>
+    <t>Setor 12</t>
+  </si>
+  <si>
+    <t>Setor 13</t>
+  </si>
+  <si>
+    <t>Setor 14</t>
+  </si>
+  <si>
+    <t>Setor 15</t>
+  </si>
+  <si>
+    <t>Setor 16</t>
+  </si>
+  <si>
+    <t>Setor 17</t>
+  </si>
+  <si>
+    <t>Setor 18</t>
+  </si>
+  <si>
+    <t>Setor 19</t>
+  </si>
+  <si>
+    <t>Setor 20</t>
   </si>
 </sst>
 </file>
@@ -370,7 +437,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +470,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -951,6 +1024,142 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088EF8FE-482E-42AC-8EA5-92878DC598D2}">
+  <dimension ref="B3:E15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>35.5</v>
+      </c>
+      <c r="D5">
+        <v>41.9</v>
+      </c>
+      <c r="E5">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D6">
+        <v>30.4</v>
+      </c>
+      <c r="E6">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10">
+        <v>4.3</v>
+      </c>
+      <c r="D10">
+        <v>3.6</v>
+      </c>
+      <c r="E10">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11">
+        <v>9.5</v>
+      </c>
+      <c r="D11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <v>0.7</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13">
+        <v>7.7</v>
+      </c>
+      <c r="D13">
+        <v>5.5</v>
+      </c>
+      <c r="E13">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14">
+        <v>5.9</v>
+      </c>
+      <c r="D14">
+        <v>1.5</v>
+      </c>
+      <c r="E14">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>3.2</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3955542-FD2E-4118-938C-50CACA7D889D}">
   <dimension ref="C3:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1019,7 +1228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B4CFF7-3A85-4820-951F-62E41E9FBB53}">
   <dimension ref="B7:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1261,7 +1470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23628D-2121-49A9-92D5-277D45F162FD}">
   <dimension ref="C3:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1398,7 +1607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB80353-2AEA-4B03-BD7E-AB8ECF39D507}">
   <dimension ref="W3:AK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4256,6 +4465,256 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098474B8-8251-4737-B9B2-B63C995DD22C}">
+  <dimension ref="B2:F23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F7" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F12" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231522F5-4F73-43C4-84CE-1220F786E75E}">
   <dimension ref="C3:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4493,7 +4952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71DEED7-F350-4CDE-A045-FE6552F7C104}">
   <dimension ref="C3:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4569,140 +5028,4 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088EF8FE-482E-42AC-8EA5-92878DC598D2}">
-  <dimension ref="B3:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5">
-        <v>35.5</v>
-      </c>
-      <c r="D5">
-        <v>41.9</v>
-      </c>
-      <c r="E5">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="D6">
-        <v>30.4</v>
-      </c>
-      <c r="E6">
-        <v>34.799999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10">
-        <v>4.3</v>
-      </c>
-      <c r="D10">
-        <v>3.6</v>
-      </c>
-      <c r="E10">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11">
-        <v>9.5</v>
-      </c>
-      <c r="D11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E11">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12">
-        <v>0.7</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13">
-        <v>7.7</v>
-      </c>
-      <c r="D13">
-        <v>5.5</v>
-      </c>
-      <c r="E13">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14">
-        <v>5.9</v>
-      </c>
-      <c r="D14">
-        <v>1.5</v>
-      </c>
-      <c r="E14">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15">
-        <v>3.2</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B88A98-8B26-43E9-83A4-B36059BA0ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01012DF-D5F2-417F-8986-A07C75BC6E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="6" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
@@ -4493,10 +4493,10 @@
         <v>105</v>
       </c>
       <c r="D4" s="8">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="F4" s="8">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="8">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="F5" s="8">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -4515,10 +4515,10 @@
         <v>107</v>
       </c>
       <c r="D6" s="8">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="8">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -4526,10 +4526,10 @@
         <v>108</v>
       </c>
       <c r="D7" s="8">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F7" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
@@ -4537,10 +4537,10 @@
         <v>109</v>
       </c>
       <c r="D8" s="8">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F8" s="8">
-        <v>0.01</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -4548,10 +4548,10 @@
         <v>110</v>
       </c>
       <c r="D9" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F9" s="8">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -4559,7 +4559,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="8">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F10" s="8">
         <v>0.05</v>
@@ -4570,10 +4570,10 @@
         <v>112</v>
       </c>
       <c r="D11" s="8">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F11" s="8">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
@@ -4584,7 +4584,7 @@
         <v>0.04</v>
       </c>
       <c r="F12" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
@@ -4592,10 +4592,10 @@
         <v>114</v>
       </c>
       <c r="D13" s="8">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F13" s="8">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
@@ -4603,10 +4603,10 @@
         <v>115</v>
       </c>
       <c r="D14" s="8">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="F14" s="8">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
@@ -4614,10 +4614,10 @@
         <v>116</v>
       </c>
       <c r="D15" s="8">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F15" s="8">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
@@ -4625,10 +4625,10 @@
         <v>117</v>
       </c>
       <c r="D16" s="8">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F16" s="8">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -4636,10 +4636,10 @@
         <v>118</v>
       </c>
       <c r="D17" s="8">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F17" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
@@ -4647,7 +4647,7 @@
         <v>119</v>
       </c>
       <c r="D18" s="8">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="F18" s="8">
         <v>0.02</v>
@@ -4658,10 +4658,10 @@
         <v>120</v>
       </c>
       <c r="D19" s="8">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="F19" s="8">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
@@ -4669,10 +4669,10 @@
         <v>121</v>
       </c>
       <c r="D20" s="8">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F20" s="8">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
@@ -4680,10 +4680,10 @@
         <v>122</v>
       </c>
       <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
         <v>0.01</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0.06</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
@@ -4691,10 +4691,10 @@
         <v>123</v>
       </c>
       <c r="D22" s="8">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F22" s="8">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
@@ -4702,10 +4702,10 @@
         <v>124</v>
       </c>
       <c r="D23" s="8">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="F23" s="8">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01012DF-D5F2-417F-8986-A07C75BC6E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22852F47-0D4C-4630-8651-A6D227D17151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="6" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="3000" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="901" activeTab="6" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -4493,10 +4493,10 @@
         <v>105</v>
       </c>
       <c r="D4" s="8">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="F4" s="8">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="8">
-        <v>0.12</v>
+        <v>0.152</v>
       </c>
       <c r="F5" s="8">
-        <v>0.12</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -4515,10 +4515,10 @@
         <v>107</v>
       </c>
       <c r="D6" s="8">
-        <v>0.1</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="F6" s="8">
-        <v>0.1</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22852F47-0D4C-4630-8651-A6D227D17151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C322D1-FB55-4514-9D32-25A46FFE5876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="901" activeTab="6" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="2" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="125">
   <si>
     <t>Labels</t>
   </si>
@@ -2027,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F8E16C-7218-4DFD-AF0C-6AD115ACF99C}">
-  <dimension ref="D2:F17"/>
+  <dimension ref="D2:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="4:6" x14ac:dyDescent="0.25">
@@ -2041,7 +2041,43 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="7" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="11" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D17" s="8">
         <v>1.68</v>
       </c>
@@ -2050,6 +2086,225 @@
       </c>
       <c r="F17" s="8">
         <v>1.69</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>826</v>
+      </c>
+      <c r="F19">
+        <v>457</v>
+      </c>
+      <c r="G19" s="3">
+        <v>-0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E20" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="F20" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E32" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.85499999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E34" s="3">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="F34" s="3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E37" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0.32600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E38" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E42" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="3">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.83099999999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E44" s="3">
+        <v>0.10300000000000001</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.10400000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.35199999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.75600000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E52" s="3">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2.8999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E53" s="3">
+        <v>0.93900000000000006</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.94799999999999995</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E54" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2.2000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E57" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E58" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.74099999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E64">
+        <v>515299</v>
+      </c>
+      <c r="F64">
+        <v>533967</v>
+      </c>
+    </row>
+    <row r="65" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E65" s="3">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F65" s="3">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E67" s="3">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0.872</v>
       </c>
     </row>
   </sheetData>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C322D1-FB55-4514-9D32-25A46FFE5876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86388D3-A9B3-4F9D-9961-37718F59542A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="2" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
   <sheets>
     <sheet name="DRE Saida 2" sheetId="18" r:id="rId1"/>
@@ -52,10 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="125">
-  <si>
-    <t>Labels</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="126">
   <si>
     <t>3T23</t>
   </si>
@@ -84,21 +81,12 @@
     <t>3T25</t>
   </si>
   <si>
-    <t>Lucro Liquido Recorrente</t>
-  </si>
-  <si>
     <t>9M24</t>
   </si>
   <si>
     <t>9M25</t>
   </si>
   <si>
-    <t>teste feito</t>
-  </si>
-  <si>
-    <t>teste 2 feito</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -132,33 +120,6 @@
     <t>3T25/3T24</t>
   </si>
   <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>9,4%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>11,1%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>16%</t>
-  </si>
-  <si>
-    <t>15,1%</t>
-  </si>
-  <si>
-    <t>12,1%</t>
-  </si>
-  <si>
-    <t>15,4%</t>
-  </si>
-  <si>
     <t>Carteira de Crédito</t>
   </si>
   <si>
@@ -427,6 +388,48 @@
   </si>
   <si>
     <t>Setor 20</t>
+  </si>
+  <si>
+    <t>Variação</t>
+  </si>
+  <si>
+    <t>4T25/3T25</t>
+  </si>
+  <si>
+    <t>4T25/4T24</t>
+  </si>
+  <si>
+    <t>2025/2024</t>
+  </si>
+  <si>
+    <t>Margem Fiannceira Com mercado</t>
+  </si>
+  <si>
+    <t>receita de prestação de serviços</t>
+  </si>
+  <si>
+    <t>custo de Crédito</t>
+  </si>
+  <si>
+    <t>Outras Receitas/Despesas</t>
+  </si>
+  <si>
+    <t>Despsas de Poessoal</t>
+  </si>
+  <si>
+    <t>Despesas Tributarias</t>
+  </si>
+  <si>
+    <t>Resultado antes da Tributacao sobre Lucro</t>
+  </si>
+  <si>
+    <t>Importo de Renta</t>
+  </si>
+  <si>
+    <t>Participacaoo de Naão controladores</t>
+  </si>
+  <si>
+    <t>LucroLiquido Recorrente</t>
   </si>
 </sst>
 </file>
@@ -503,7 +506,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -520,6 +523,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -864,13 +870,13 @@
   <sheetData>
     <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>2024</v>
@@ -881,7 +887,7 @@
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>3214</v>
@@ -901,7 +907,7 @@
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>2519</v>
@@ -921,7 +927,7 @@
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>2367</v>
@@ -941,7 +947,7 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>152</v>
@@ -961,7 +967,7 @@
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D9">
         <v>695</v>
@@ -1033,18 +1039,18 @@
   <sheetData>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>35.5</v>
@@ -1058,7 +1064,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>34.799999999999997</v>
@@ -1072,7 +1078,7 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C10">
         <v>4.3</v>
@@ -1086,7 +1092,7 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>9.5</v>
@@ -1100,7 +1106,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>0.7</v>
@@ -1114,7 +1120,7 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C13">
         <v>7.7</v>
@@ -1128,7 +1134,7 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <v>5.9</v>
@@ -1142,7 +1148,7 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <v>3.2</v>
@@ -1166,13 +1172,13 @@
   <sheetData>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="3:7" x14ac:dyDescent="0.25">
@@ -1235,7 +1241,7 @@
   <sheetData>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1282,7 +1288,7 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1329,7 +1335,7 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1376,7 +1382,7 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -1481,26 +1487,26 @@
   <sheetData>
     <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="G4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>169</v>
@@ -1520,7 +1526,7 @@
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>4167</v>
@@ -1540,7 +1546,7 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>513</v>
@@ -1560,7 +1566,7 @@
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>4032</v>
@@ -1580,7 +1586,7 @@
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>8881</v>
@@ -1614,37 +1620,37 @@
   <sheetData>
     <row r="3" spans="23:37" x14ac:dyDescent="0.25">
       <c r="W3" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" t="s">
         <v>1</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>2</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>3</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>4</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>5</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>6</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>8</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AJ3" t="s">
         <v>9</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>11</v>
-      </c>
       <c r="AK3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="23:37" x14ac:dyDescent="0.25">
@@ -1697,16 +1703,16 @@
   <sheetData>
     <row r="2" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>2024</v>
@@ -1717,7 +1723,7 @@
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>187</v>
@@ -1746,7 +1752,7 @@
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D9">
         <v>776</v>
@@ -1775,7 +1781,7 @@
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3">
         <v>3.4000000000000002E-2</v>
@@ -1824,13 +1830,13 @@
     </row>
     <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G16">
         <v>2024</v>
@@ -1844,7 +1850,7 @@
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>239</v>
@@ -1864,7 +1870,7 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D26">
         <v>695</v>
@@ -1884,7 +1890,7 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D28">
         <v>457</v>
@@ -1907,13 +1913,13 @@
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G33">
         <v>2024</v>
@@ -1924,7 +1930,7 @@
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D35">
         <v>520</v>
@@ -1944,7 +1950,7 @@
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D39">
         <v>398</v>
@@ -1964,7 +1970,7 @@
     </row>
     <row r="45" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D45">
         <v>98</v>
@@ -1993,7 +1999,7 @@
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D47">
         <v>1015</v>
@@ -2032,13 +2038,13 @@
   <sheetData>
     <row r="2" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="4:6" x14ac:dyDescent="0.25">
@@ -2109,10 +2115,10 @@
     </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="4:7" x14ac:dyDescent="0.25">
@@ -2141,10 +2147,10 @@
     </row>
     <row r="35" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="5:6" x14ac:dyDescent="0.25">
@@ -2165,10 +2171,10 @@
     </row>
     <row r="40" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="5:6" x14ac:dyDescent="0.25">
@@ -2197,10 +2203,10 @@
     </row>
     <row r="45" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="5:6" x14ac:dyDescent="0.25">
@@ -2221,10 +2227,10 @@
     </row>
     <row r="50" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="5:6" x14ac:dyDescent="0.25">
@@ -2253,10 +2259,10 @@
     </row>
     <row r="55" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="5:6" x14ac:dyDescent="0.25">
@@ -2277,10 +2283,10 @@
     </row>
     <row r="61" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="5:6" x14ac:dyDescent="0.25">
@@ -2316,168 +2322,491 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417E299C-E79D-4FD4-B55D-DB1E7B3327CE}">
   <dimension ref="B3:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>285</v>
+        <v>45</v>
+      </c>
+      <c r="G3">
+        <v>2024</v>
+      </c>
+      <c r="H3">
+        <v>2025</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>3214</v>
+      </c>
+      <c r="E5">
+        <v>2919</v>
+      </c>
+      <c r="F5">
+        <v>3136</v>
+      </c>
+      <c r="G5">
+        <v>11980</v>
+      </c>
+      <c r="H5">
+        <v>11913</v>
+      </c>
+      <c r="I5">
+        <v>7.4</v>
+      </c>
+      <c r="J5">
+        <v>-2.4</v>
+      </c>
+      <c r="K5">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>2519</v>
+      </c>
+      <c r="E6">
+        <v>2295</v>
+      </c>
+      <c r="F6">
+        <v>3215165</v>
+      </c>
+      <c r="G6">
+        <v>651</v>
+      </c>
+      <c r="H6">
+        <v>65</v>
+      </c>
+      <c r="I6">
+        <v>7.4</v>
+      </c>
+      <c r="J6">
+        <v>-2.4</v>
+      </c>
+      <c r="K6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>1824</v>
+      </c>
+      <c r="E7">
+        <v>1671</v>
+      </c>
+      <c r="F7">
+        <v>6427194</v>
+      </c>
+      <c r="G7">
+        <v>-10678</v>
+      </c>
+      <c r="H7">
+        <v>-11783</v>
+      </c>
+      <c r="I7">
+        <v>7.4</v>
+      </c>
+      <c r="J7">
+        <v>-2.4</v>
+      </c>
+      <c r="K7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8">
+        <v>1129</v>
+      </c>
+      <c r="E8">
+        <v>1047</v>
+      </c>
+      <c r="F8">
+        <v>9639223</v>
+      </c>
+      <c r="G8">
+        <v>-22007</v>
+      </c>
+      <c r="H8">
+        <v>-23631</v>
+      </c>
+      <c r="I8">
+        <v>7.4</v>
+      </c>
+      <c r="J8">
+        <v>-2.4</v>
+      </c>
+      <c r="K8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9">
+        <v>434</v>
+      </c>
+      <c r="E9">
+        <v>423</v>
+      </c>
+      <c r="F9">
+        <v>12851252</v>
+      </c>
+      <c r="G9">
+        <v>-33336</v>
+      </c>
+      <c r="H9">
+        <v>-35479</v>
+      </c>
+      <c r="I9">
+        <v>7.4</v>
+      </c>
+      <c r="J9">
+        <v>-2.4</v>
+      </c>
+      <c r="K9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10">
+        <v>-261</v>
+      </c>
+      <c r="E10">
+        <v>-201</v>
+      </c>
+      <c r="F10">
+        <v>16063281</v>
+      </c>
+      <c r="G10">
+        <v>-44665</v>
+      </c>
+      <c r="H10">
+        <v>-47327</v>
+      </c>
+      <c r="I10">
+        <v>7.4</v>
+      </c>
+      <c r="J10">
+        <v>-2.4</v>
+      </c>
+      <c r="K10">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11">
+        <v>-956</v>
+      </c>
+      <c r="E11">
+        <v>-825</v>
+      </c>
+      <c r="F11">
+        <v>19275310</v>
+      </c>
+      <c r="G11">
+        <v>-55994</v>
+      </c>
+      <c r="H11">
+        <v>-59175</v>
+      </c>
+      <c r="I11">
+        <v>7.4</v>
+      </c>
+      <c r="J11">
+        <v>-2.4</v>
+      </c>
+      <c r="K11">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12">
+        <v>-1651</v>
+      </c>
+      <c r="E12">
+        <v>-1449</v>
+      </c>
+      <c r="F12">
+        <v>22487339</v>
+      </c>
+      <c r="G12">
+        <v>-67323</v>
+      </c>
+      <c r="H12">
+        <v>-71023</v>
+      </c>
+      <c r="I12">
+        <v>7.4</v>
+      </c>
+      <c r="J12">
+        <v>-2.4</v>
+      </c>
+      <c r="K12">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13">
+        <v>-2346</v>
+      </c>
+      <c r="E13">
+        <v>-2073</v>
+      </c>
+      <c r="F13">
+        <v>25699368</v>
+      </c>
+      <c r="G13">
+        <v>-78652</v>
+      </c>
+      <c r="H13">
+        <v>-82871</v>
+      </c>
+      <c r="I13">
+        <v>7.4</v>
+      </c>
+      <c r="J13">
+        <v>-2.4</v>
+      </c>
+      <c r="K13">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14">
+        <v>-3041</v>
+      </c>
+      <c r="E14">
+        <v>-2697</v>
+      </c>
+      <c r="F14">
+        <v>28911397</v>
+      </c>
+      <c r="G14">
+        <v>-89981</v>
+      </c>
+      <c r="H14">
+        <v>-94719</v>
+      </c>
+      <c r="I14">
+        <v>7.4</v>
+      </c>
+      <c r="J14">
+        <v>-2.4</v>
+      </c>
+      <c r="K14">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15">
+        <v>-3736</v>
+      </c>
+      <c r="E15">
+        <v>-3321</v>
+      </c>
+      <c r="F15">
+        <v>32123426</v>
+      </c>
+      <c r="G15">
+        <v>-101310</v>
+      </c>
+      <c r="H15">
+        <v>-106567</v>
+      </c>
+      <c r="I15">
+        <v>7.4</v>
+      </c>
+      <c r="J15">
+        <v>-2.4</v>
+      </c>
+      <c r="K15">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16">
+        <v>-4431</v>
+      </c>
+      <c r="E16">
+        <v>-3945</v>
+      </c>
+      <c r="F16">
+        <v>35335455</v>
+      </c>
+      <c r="G16">
+        <v>-112639</v>
+      </c>
+      <c r="H16">
+        <v>-118415</v>
+      </c>
+      <c r="I16">
+        <v>7.4</v>
+      </c>
+      <c r="J16">
+        <v>-2.4</v>
+      </c>
+      <c r="K16">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17">
+        <v>-5126</v>
+      </c>
+      <c r="E17">
+        <v>-4569</v>
+      </c>
+      <c r="F17">
+        <v>38547484</v>
+      </c>
+      <c r="G17">
+        <v>-123968</v>
+      </c>
+      <c r="H17">
+        <v>-130263</v>
+      </c>
+      <c r="I17">
+        <v>7.4</v>
+      </c>
+      <c r="J17">
+        <v>-2.4</v>
+      </c>
+      <c r="K17">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>125</v>
       </c>
       <c r="D18">
-        <v>302</v>
+        <v>-5821</v>
       </c>
       <c r="E18">
-        <v>321</v>
+        <v>-5193</v>
       </c>
       <c r="F18">
-        <v>363</v>
+        <v>41759513</v>
       </c>
       <c r="G18">
-        <v>496</v>
+        <v>-135297</v>
       </c>
       <c r="H18">
-        <v>542</v>
+        <v>-142111</v>
       </c>
       <c r="I18">
-        <v>480</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>459</v>
+        <v>-2.4</v>
       </c>
       <c r="K18">
-        <v>461</v>
-      </c>
-      <c r="L18">
-        <v>1180</v>
-      </c>
-      <c r="M18">
-        <v>1400</v>
+        <v>-0.6</v>
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="L21" s="1"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="4">
-        <v>0.09</v>
-      </c>
-      <c r="D25" s="5">
-        <v>9.4E-2</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0.111</v>
-      </c>
-      <c r="G25" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="H25" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="I25" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="J25" s="5">
-        <v>0.151</v>
-      </c>
-      <c r="K25" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="L25" s="5">
-        <v>0.121</v>
-      </c>
-      <c r="M25" s="5">
-        <v>0.154</v>
-      </c>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B35" s="2"/>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B36" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I3:K3"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2495,24 +2824,24 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>44.495999999999995</v>
@@ -2522,15 +2851,15 @@
         <v>0.47999999999999987</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>13.904999999999998</v>
@@ -2540,19 +2869,19 @@
         <v>0.14999999999999994</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N3" s="3">
         <v>-0.13300000000000001</v>
@@ -2560,10 +2889,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>10.196999999999999</v>
@@ -2593,10 +2922,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>0.92699999999999994</v>
@@ -2611,10 +2940,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>2.7809999999999997</v>
@@ -2626,10 +2955,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>4.6349999999999998</v>
@@ -2641,10 +2970,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>4.6349999999999998</v>
@@ -2656,10 +2985,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>3.7079999999999997</v>
@@ -2671,10 +3000,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>7.4159999999999995</v>
@@ -2684,7 +3013,7 @@
         <v>7.9999999999999974E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -4353,21 +4682,21 @@
   <sheetData>
     <row r="12" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="3:6" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="9" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D14" s="9">
         <v>61464</v>
@@ -4381,7 +4710,7 @@
     </row>
     <row r="15" spans="3:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C15" s="9" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D15" s="9">
         <v>52789</v>
@@ -4395,7 +4724,7 @@
     </row>
     <row r="16" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D16">
         <v>42236</v>
@@ -4409,7 +4738,7 @@
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D17">
         <v>2219</v>
@@ -4423,7 +4752,7 @@
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>3548</v>
@@ -4437,7 +4766,7 @@
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D19">
         <v>4167</v>
@@ -4451,7 +4780,7 @@
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>513</v>
@@ -4465,7 +4794,7 @@
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>106</v>
@@ -4479,7 +4808,7 @@
     </row>
     <row r="22" spans="3:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C22" s="9" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D22" s="9">
         <v>8857</v>
@@ -4493,7 +4822,7 @@
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>4032</v>
@@ -4507,7 +4836,7 @@
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>4765</v>
@@ -4521,7 +4850,7 @@
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D25">
         <v>60</v>
@@ -4537,7 +4866,7 @@
     <row r="26" spans="3:14" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C27" s="9" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D27" s="9">
         <v>12884</v>
@@ -4551,7 +4880,7 @@
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D28">
         <v>6426</v>
@@ -4565,7 +4894,7 @@
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D29">
         <v>5114</v>
@@ -4579,7 +4908,7 @@
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>1343</v>
@@ -4593,7 +4922,7 @@
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C34" s="9" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D34" s="9">
         <v>28856</v>
@@ -4607,7 +4936,7 @@
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D35">
         <v>6008</v>
@@ -4621,7 +4950,7 @@
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D36">
         <v>9964</v>
@@ -4635,7 +4964,7 @@
     </row>
     <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D40">
         <v>90502</v>
@@ -4649,18 +4978,18 @@
     </row>
     <row r="115" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D115" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F115" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D117">
         <v>14043</v>
@@ -4674,7 +5003,7 @@
     </row>
     <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D118">
         <v>11864</v>
@@ -4688,7 +5017,7 @@
     </row>
     <row r="119" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C119" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D119">
         <v>2948</v>
@@ -4702,7 +5031,7 @@
     </row>
     <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D120">
         <v>28856</v>
@@ -4726,26 +5055,26 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D4" s="8">
         <v>0.125</v>
@@ -4756,7 +5085,7 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D5" s="8">
         <v>0.152</v>
@@ -4767,7 +5096,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D6" s="8">
         <v>0.10299999999999999</v>
@@ -4778,7 +5107,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D7" s="8">
         <v>0.08</v>
@@ -4789,7 +5118,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D8" s="8">
         <v>7.0000000000000007E-2</v>
@@ -4800,7 +5129,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D9" s="8">
         <v>0.05</v>
@@ -4811,7 +5140,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D10" s="8">
         <v>0.05</v>
@@ -4822,7 +5151,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D11" s="8">
         <v>0.04</v>
@@ -4833,7 +5162,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" s="8">
         <v>0.04</v>
@@ -4844,7 +5173,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D13" s="8">
         <v>0.03</v>
@@ -4855,7 +5184,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D14" s="8">
         <v>0.03</v>
@@ -4866,7 +5195,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D15" s="8">
         <v>0.03</v>
@@ -4877,7 +5206,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D16" s="8">
         <v>0.02</v>
@@ -4888,7 +5217,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D17" s="8">
         <v>0.02</v>
@@ -4899,7 +5228,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="D18" s="8">
         <v>0.02</v>
@@ -4910,7 +5239,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D19" s="8">
         <v>0.01</v>
@@ -4921,7 +5250,7 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D20" s="8">
         <v>0.01</v>
@@ -4932,7 +5261,7 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D21" s="8">
         <v>0</v>
@@ -4943,7 +5272,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D22" s="8">
         <v>0.01</v>
@@ -4954,7 +5283,7 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D23" s="8">
         <v>0.13</v>
@@ -4979,13 +5308,13 @@
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>2024</v>
@@ -4996,7 +5325,7 @@
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3">
         <v>0.28799999999999998</v>
@@ -5016,7 +5345,7 @@
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D6">
         <v>49</v>
@@ -5036,7 +5365,7 @@
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>40.700000000000003</v>
@@ -5056,7 +5385,7 @@
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>85.8</v>
@@ -5076,7 +5405,7 @@
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>7.1</v>
@@ -5096,7 +5425,7 @@
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D10">
         <v>6.1260000000000003</v>
@@ -5117,7 +5446,7 @@
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D11">
         <v>1.0109999999999999</v>
@@ -5137,18 +5466,18 @@
     </row>
     <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D20">
         <v>48</v>
@@ -5162,7 +5491,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D21">
         <v>42.235999999999997</v>
@@ -5176,7 +5505,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D22">
         <v>2.2189999999999999</v>
@@ -5190,7 +5519,7 @@
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D23">
         <v>3.548</v>
@@ -5214,13 +5543,13 @@
   <sheetData>
     <row r="3" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>2024</v>
@@ -5231,7 +5560,7 @@
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>420</v>
@@ -5252,23 +5581,23 @@
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>4761</v>

--- a/testing.xlsx
+++ b/testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\renato\projetos\double-projects\ppt-doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86388D3-A9B3-4F9D-9961-37718F59542A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1213294C-F199-46B3-A1F9-792514270085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{E2EAAA9B-09FC-4773-92F8-622FD93420C8}"/>
   </bookViews>
@@ -2328,19 +2328,19 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D3" t="s">
+      <c r="D3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="14">
         <v>2024</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="14">
         <v>2025</v>
       </c>
       <c r="I3" s="14" t="s">
@@ -2350,6 +2350,11 @@
       <c r="K3" s="14"/>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
       <c r="I4" t="s">
         <v>113</v>
       </c>
@@ -2803,8 +2808,13 @@
       <c r="B36" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="I3:K3"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
